--- a/artfynd/A 40423-2025 artfynd.xlsx
+++ b/artfynd/A 40423-2025 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>128105195</v>
       </c>
       <c r="B3" t="n">
-        <v>91367</v>
+        <v>91368</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>128105178</v>
       </c>
       <c r="B4" t="n">
-        <v>91349</v>
+        <v>91350</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>128105177</v>
       </c>
       <c r="B5" t="n">
-        <v>91349</v>
+        <v>91350</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>128105182</v>
       </c>
       <c r="B6" t="n">
-        <v>98488</v>
+        <v>98489</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1165,32 +1165,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128105191</v>
+        <v>128105176</v>
       </c>
       <c r="B7" t="n">
-        <v>98467</v>
+        <v>91350</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1200,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>742729</v>
+        <v>742883</v>
       </c>
       <c r="R7" t="n">
-        <v>7197803</v>
+        <v>7197635</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1265,7 +1265,7 @@
         <v>128105183</v>
       </c>
       <c r="B8" t="n">
-        <v>98488</v>
+        <v>98489</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1359,32 +1359,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128105176</v>
+        <v>128105191</v>
       </c>
       <c r="B9" t="n">
-        <v>91349</v>
+        <v>98468</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1394,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>742883</v>
+        <v>742729</v>
       </c>
       <c r="R9" t="n">
-        <v>7197635</v>
+        <v>7197803</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1553,32 +1553,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128105193</v>
+        <v>128105198</v>
       </c>
       <c r="B11" t="n">
-        <v>98467</v>
+        <v>79029</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1588,10 +1588,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>742919</v>
+        <v>743076</v>
       </c>
       <c r="R11" t="n">
-        <v>7197599</v>
+        <v>7197586</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1650,32 +1650,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128105198</v>
+        <v>128105193</v>
       </c>
       <c r="B12" t="n">
-        <v>79029</v>
+        <v>98468</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1685,10 +1685,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>743076</v>
+        <v>742919</v>
       </c>
       <c r="R12" t="n">
-        <v>7197586</v>
+        <v>7197599</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1750,7 +1750,7 @@
         <v>128105190</v>
       </c>
       <c r="B13" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2916,32 +2916,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128105197</v>
+        <v>128105187</v>
       </c>
       <c r="B25" t="n">
-        <v>79029</v>
+        <v>98468</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2951,10 +2951,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>742882</v>
+        <v>742851</v>
       </c>
       <c r="R25" t="n">
-        <v>7197625</v>
+        <v>7197885</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3013,10 +3013,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128105187</v>
+        <v>128105189</v>
       </c>
       <c r="B26" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3048,10 +3048,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>742851</v>
+        <v>742836</v>
       </c>
       <c r="R26" t="n">
-        <v>7197885</v>
+        <v>7197877</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3110,32 +3110,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128105189</v>
+        <v>128105197</v>
       </c>
       <c r="B27" t="n">
-        <v>98467</v>
+        <v>79029</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3145,10 +3145,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>742836</v>
+        <v>742882</v>
       </c>
       <c r="R27" t="n">
-        <v>7197877</v>
+        <v>7197625</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>

--- a/artfynd/A 40423-2025 artfynd.xlsx
+++ b/artfynd/A 40423-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128105199</v>
+        <v>128105195</v>
       </c>
       <c r="B2" t="n">
-        <v>79029</v>
+        <v>91368</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>743059</v>
+        <v>742779</v>
       </c>
       <c r="R2" t="n">
-        <v>7197601</v>
+        <v>7197609</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-08-28</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128105195</v>
+        <v>128105178</v>
       </c>
       <c r="B3" t="n">
-        <v>91368</v>
+        <v>91350</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>742779</v>
+        <v>743047</v>
       </c>
       <c r="R3" t="n">
-        <v>7197609</v>
+        <v>7197522</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -874,7 +869,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128105178</v>
+        <v>128105177</v>
       </c>
       <c r="B4" t="n">
         <v>91350</v>
@@ -909,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>743047</v>
+        <v>743033</v>
       </c>
       <c r="R4" t="n">
-        <v>7197522</v>
+        <v>7197526</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -971,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128105177</v>
+        <v>128105199</v>
       </c>
       <c r="B5" t="n">
-        <v>91350</v>
+        <v>79029</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -982,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>743033</v>
+        <v>743059</v>
       </c>
       <c r="R5" t="n">
-        <v>7197526</v>
+        <v>7197601</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1042,6 +1037,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1262,32 +1262,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128105183</v>
+        <v>128105205</v>
       </c>
       <c r="B8" t="n">
-        <v>98489</v>
+        <v>79029</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>742778</v>
+        <v>742831</v>
       </c>
       <c r="R8" t="n">
-        <v>7197616</v>
+        <v>7197554</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1456,32 +1456,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128105205</v>
+        <v>128105183</v>
       </c>
       <c r="B10" t="n">
-        <v>79029</v>
+        <v>98489</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1491,10 +1491,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>742831</v>
+        <v>742778</v>
       </c>
       <c r="R10" t="n">
-        <v>7197554</v>
+        <v>7197616</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -2426,7 +2426,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128105207</v>
+        <v>128105200</v>
       </c>
       <c r="B20" t="n">
         <v>79029</v>
@@ -2461,10 +2461,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>743058</v>
+        <v>743052</v>
       </c>
       <c r="R20" t="n">
-        <v>7197514</v>
+        <v>7197729</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2497,11 +2497,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-08-28</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2528,7 +2523,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128105200</v>
+        <v>128105207</v>
       </c>
       <c r="B21" t="n">
         <v>79029</v>
@@ -2563,10 +2558,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>743052</v>
+        <v>743058</v>
       </c>
       <c r="R21" t="n">
-        <v>7197729</v>
+        <v>7197514</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2599,6 +2594,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2916,32 +2916,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128105187</v>
+        <v>128105197</v>
       </c>
       <c r="B25" t="n">
-        <v>98468</v>
+        <v>79029</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2951,10 +2951,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>742851</v>
+        <v>742882</v>
       </c>
       <c r="R25" t="n">
-        <v>7197885</v>
+        <v>7197625</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3013,7 +3013,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128105189</v>
+        <v>128105187</v>
       </c>
       <c r="B26" t="n">
         <v>98468</v>
@@ -3048,10 +3048,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>742836</v>
+        <v>742851</v>
       </c>
       <c r="R26" t="n">
-        <v>7197877</v>
+        <v>7197885</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3110,32 +3110,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128105197</v>
+        <v>128105189</v>
       </c>
       <c r="B27" t="n">
-        <v>79029</v>
+        <v>98468</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3145,10 +3145,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>742882</v>
+        <v>742836</v>
       </c>
       <c r="R27" t="n">
-        <v>7197625</v>
+        <v>7197877</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>

--- a/artfynd/A 40423-2025 artfynd.xlsx
+++ b/artfynd/A 40423-2025 artfynd.xlsx
@@ -1553,32 +1553,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128105198</v>
+        <v>128105190</v>
       </c>
       <c r="B11" t="n">
-        <v>79029</v>
+        <v>98470</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1588,10 +1588,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>743076</v>
+        <v>743078</v>
       </c>
       <c r="R11" t="n">
-        <v>7197586</v>
+        <v>7197587</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1747,32 +1747,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128105190</v>
+        <v>128105198</v>
       </c>
       <c r="B13" t="n">
-        <v>98470</v>
+        <v>79029</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>743078</v>
+        <v>743076</v>
       </c>
       <c r="R13" t="n">
-        <v>7197587</v>
+        <v>7197586</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2038,32 +2038,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128105203</v>
+        <v>128105181</v>
       </c>
       <c r="B16" t="n">
-        <v>79029</v>
+        <v>80161</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2073,10 +2073,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>742924</v>
+        <v>742967</v>
       </c>
       <c r="R16" t="n">
-        <v>7197844</v>
+        <v>7197575</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2135,32 +2135,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128105181</v>
+        <v>128105203</v>
       </c>
       <c r="B17" t="n">
-        <v>80161</v>
+        <v>79029</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2170,10 +2170,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>742967</v>
+        <v>742924</v>
       </c>
       <c r="R17" t="n">
-        <v>7197575</v>
+        <v>7197844</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>

--- a/artfynd/A 40423-2025 artfynd.xlsx
+++ b/artfynd/A 40423-2025 artfynd.xlsx
@@ -1262,32 +1262,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128105191</v>
+        <v>128105176</v>
       </c>
       <c r="B8" t="n">
-        <v>98470</v>
+        <v>91352</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>742729</v>
+        <v>742883</v>
       </c>
       <c r="R8" t="n">
-        <v>7197803</v>
+        <v>7197635</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1359,32 +1359,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128105183</v>
+        <v>128105191</v>
       </c>
       <c r="B9" t="n">
-        <v>98491</v>
+        <v>98470</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1394,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>742778</v>
+        <v>742729</v>
       </c>
       <c r="R9" t="n">
-        <v>7197616</v>
+        <v>7197803</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1456,32 +1456,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128105176</v>
+        <v>128105183</v>
       </c>
       <c r="B10" t="n">
-        <v>91352</v>
+        <v>98491</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>221952</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1491,10 +1491,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>742883</v>
+        <v>742778</v>
       </c>
       <c r="R10" t="n">
-        <v>7197635</v>
+        <v>7197616</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 40423-2025 artfynd.xlsx
+++ b/artfynd/A 40423-2025 artfynd.xlsx
@@ -2038,32 +2038,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128105181</v>
+        <v>128105203</v>
       </c>
       <c r="B16" t="n">
-        <v>80161</v>
+        <v>79029</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2073,10 +2073,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>742967</v>
+        <v>742924</v>
       </c>
       <c r="R16" t="n">
-        <v>7197575</v>
+        <v>7197844</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2135,32 +2135,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128105203</v>
+        <v>128105181</v>
       </c>
       <c r="B17" t="n">
-        <v>79029</v>
+        <v>80161</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2170,10 +2170,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>742924</v>
+        <v>742967</v>
       </c>
       <c r="R17" t="n">
-        <v>7197844</v>
+        <v>7197575</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>

--- a/artfynd/A 40423-2025 artfynd.xlsx
+++ b/artfynd/A 40423-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128105178</v>
+        <v>128105199</v>
       </c>
       <c r="B2" t="n">
-        <v>91352</v>
+        <v>79032</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>743047</v>
+        <v>743059</v>
       </c>
       <c r="R2" t="n">
-        <v>7197522</v>
+        <v>7197601</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,6 +746,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128105177</v>
+        <v>128105178</v>
       </c>
       <c r="B3" t="n">
-        <v>91352</v>
+        <v>91360</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>743033</v>
+        <v>743047</v>
       </c>
       <c r="R3" t="n">
-        <v>7197526</v>
+        <v>7197522</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128105195</v>
+        <v>128105177</v>
       </c>
       <c r="B4" t="n">
-        <v>91370</v>
+        <v>91360</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +885,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>742779</v>
+        <v>743033</v>
       </c>
       <c r="R4" t="n">
-        <v>7197609</v>
+        <v>7197526</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128105199</v>
+        <v>128105195</v>
       </c>
       <c r="B5" t="n">
-        <v>79029</v>
+        <v>91378</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +982,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>743059</v>
+        <v>742779</v>
       </c>
       <c r="R5" t="n">
-        <v>7197601</v>
+        <v>7197609</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1037,11 +1042,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-28</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1071,7 +1071,7 @@
         <v>128105182</v>
       </c>
       <c r="B6" t="n">
-        <v>98491</v>
+        <v>98499</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1165,10 +1165,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128105205</v>
+        <v>128105176</v>
       </c>
       <c r="B7" t="n">
-        <v>79029</v>
+        <v>91360</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1176,21 +1176,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1200,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>742831</v>
+        <v>742883</v>
       </c>
       <c r="R7" t="n">
-        <v>7197554</v>
+        <v>7197635</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1262,32 +1262,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128105176</v>
+        <v>128105191</v>
       </c>
       <c r="B8" t="n">
-        <v>91352</v>
+        <v>98478</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>742883</v>
+        <v>742729</v>
       </c>
       <c r="R8" t="n">
-        <v>7197635</v>
+        <v>7197803</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1359,32 +1359,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128105191</v>
+        <v>128105205</v>
       </c>
       <c r="B9" t="n">
-        <v>98470</v>
+        <v>79032</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1394,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>742729</v>
+        <v>742831</v>
       </c>
       <c r="R9" t="n">
-        <v>7197803</v>
+        <v>7197554</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1459,7 +1459,7 @@
         <v>128105183</v>
       </c>
       <c r="B10" t="n">
-        <v>98491</v>
+        <v>98499</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
         <v>128105190</v>
       </c>
       <c r="B11" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1650,32 +1650,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128105193</v>
+        <v>128105198</v>
       </c>
       <c r="B12" t="n">
-        <v>98470</v>
+        <v>79032</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1685,10 +1685,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>742919</v>
+        <v>743076</v>
       </c>
       <c r="R12" t="n">
-        <v>7197599</v>
+        <v>7197586</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1747,32 +1747,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128105198</v>
+        <v>128105193</v>
       </c>
       <c r="B13" t="n">
-        <v>79029</v>
+        <v>98478</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>743076</v>
+        <v>742919</v>
       </c>
       <c r="R13" t="n">
-        <v>7197586</v>
+        <v>7197599</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1847,7 +1847,7 @@
         <v>128105206</v>
       </c>
       <c r="B14" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>128105202</v>
       </c>
       <c r="B15" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2038,32 +2038,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128105203</v>
+        <v>128105181</v>
       </c>
       <c r="B16" t="n">
-        <v>79029</v>
+        <v>80164</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2073,10 +2073,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>742924</v>
+        <v>742967</v>
       </c>
       <c r="R16" t="n">
-        <v>7197844</v>
+        <v>7197575</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2135,32 +2135,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128105181</v>
+        <v>128105203</v>
       </c>
       <c r="B17" t="n">
-        <v>80161</v>
+        <v>79032</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2170,10 +2170,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>742967</v>
+        <v>742924</v>
       </c>
       <c r="R17" t="n">
-        <v>7197575</v>
+        <v>7197844</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2235,7 +2235,7 @@
         <v>128105201</v>
       </c>
       <c r="B18" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2332,7 +2332,7 @@
         <v>128105196</v>
       </c>
       <c r="B19" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2429,7 +2429,7 @@
         <v>128105207</v>
       </c>
       <c r="B20" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2531,7 +2531,7 @@
         <v>128105200</v>
       </c>
       <c r="B21" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2628,7 +2628,7 @@
         <v>128105180</v>
       </c>
       <c r="B22" t="n">
-        <v>57832</v>
+        <v>57833</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2725,7 +2725,7 @@
         <v>128105204</v>
       </c>
       <c r="B23" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2822,7 +2822,7 @@
         <v>128105208</v>
       </c>
       <c r="B24" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2916,32 +2916,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128105197</v>
+        <v>128105187</v>
       </c>
       <c r="B25" t="n">
-        <v>79029</v>
+        <v>98478</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2951,10 +2951,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>742882</v>
+        <v>742851</v>
       </c>
       <c r="R25" t="n">
-        <v>7197625</v>
+        <v>7197885</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3013,10 +3013,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128105187</v>
+        <v>128105189</v>
       </c>
       <c r="B26" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3048,10 +3048,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>742851</v>
+        <v>742836</v>
       </c>
       <c r="R26" t="n">
-        <v>7197885</v>
+        <v>7197877</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3110,32 +3110,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128105189</v>
+        <v>128105197</v>
       </c>
       <c r="B27" t="n">
-        <v>98470</v>
+        <v>79032</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3145,10 +3145,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>742836</v>
+        <v>742882</v>
       </c>
       <c r="R27" t="n">
-        <v>7197877</v>
+        <v>7197625</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3210,7 +3210,7 @@
         <v>128105209</v>
       </c>
       <c r="B28" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
         <v>128105184</v>
       </c>
       <c r="B29" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 40423-2025 artfynd.xlsx
+++ b/artfynd/A 40423-2025 artfynd.xlsx
@@ -1359,32 +1359,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128105205</v>
+        <v>128105183</v>
       </c>
       <c r="B9" t="n">
-        <v>79032</v>
+        <v>98499</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1394,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>742831</v>
+        <v>742778</v>
       </c>
       <c r="R9" t="n">
-        <v>7197554</v>
+        <v>7197616</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1456,32 +1456,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128105183</v>
+        <v>128105205</v>
       </c>
       <c r="B10" t="n">
-        <v>98499</v>
+        <v>79032</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1491,10 +1491,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>742778</v>
+        <v>742831</v>
       </c>
       <c r="R10" t="n">
-        <v>7197616</v>
+        <v>7197554</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 40423-2025 artfynd.xlsx
+++ b/artfynd/A 40423-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128105199</v>
       </c>
       <c r="B2" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128105178</v>
+        <v>128105195</v>
       </c>
       <c r="B3" t="n">
-        <v>91360</v>
+        <v>91470</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>743047</v>
+        <v>742779</v>
       </c>
       <c r="R3" t="n">
-        <v>7197522</v>
+        <v>7197609</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -874,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128105177</v>
+        <v>128105178</v>
       </c>
       <c r="B4" t="n">
-        <v>91360</v>
+        <v>91452</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -909,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>743033</v>
+        <v>743047</v>
       </c>
       <c r="R4" t="n">
-        <v>7197526</v>
+        <v>7197522</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -971,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128105195</v>
+        <v>128105177</v>
       </c>
       <c r="B5" t="n">
-        <v>91378</v>
+        <v>91452</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -982,21 +982,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>742779</v>
+        <v>743033</v>
       </c>
       <c r="R5" t="n">
-        <v>7197609</v>
+        <v>7197526</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,7 +1071,7 @@
         <v>128105182</v>
       </c>
       <c r="B6" t="n">
-        <v>98499</v>
+        <v>98592</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         <v>128105176</v>
       </c>
       <c r="B7" t="n">
-        <v>91360</v>
+        <v>91452</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1262,32 +1262,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128105191</v>
+        <v>128105205</v>
       </c>
       <c r="B8" t="n">
-        <v>98478</v>
+        <v>79083</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>742729</v>
+        <v>742831</v>
       </c>
       <c r="R8" t="n">
-        <v>7197803</v>
+        <v>7197554</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1359,32 +1359,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128105183</v>
+        <v>128105191</v>
       </c>
       <c r="B9" t="n">
-        <v>98499</v>
+        <v>98571</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1394,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>742778</v>
+        <v>742729</v>
       </c>
       <c r="R9" t="n">
-        <v>7197616</v>
+        <v>7197803</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1456,32 +1456,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128105205</v>
+        <v>128105183</v>
       </c>
       <c r="B10" t="n">
-        <v>79032</v>
+        <v>98592</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1491,10 +1491,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>742831</v>
+        <v>742778</v>
       </c>
       <c r="R10" t="n">
-        <v>7197554</v>
+        <v>7197616</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1553,32 +1553,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128105190</v>
+        <v>128105198</v>
       </c>
       <c r="B11" t="n">
-        <v>98478</v>
+        <v>79083</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1588,10 +1588,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>743078</v>
+        <v>743076</v>
       </c>
       <c r="R11" t="n">
-        <v>7197587</v>
+        <v>7197586</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1650,32 +1650,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128105198</v>
+        <v>128105193</v>
       </c>
       <c r="B12" t="n">
-        <v>79032</v>
+        <v>98571</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1685,10 +1685,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>743076</v>
+        <v>742919</v>
       </c>
       <c r="R12" t="n">
-        <v>7197586</v>
+        <v>7197599</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1747,10 +1747,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128105193</v>
+        <v>128105190</v>
       </c>
       <c r="B13" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>742919</v>
+        <v>743078</v>
       </c>
       <c r="R13" t="n">
-        <v>7197599</v>
+        <v>7197587</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1847,7 +1847,7 @@
         <v>128105206</v>
       </c>
       <c r="B14" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>128105202</v>
       </c>
       <c r="B15" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2038,32 +2038,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128105181</v>
+        <v>128105203</v>
       </c>
       <c r="B16" t="n">
-        <v>80164</v>
+        <v>79083</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2073,10 +2073,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>742967</v>
+        <v>742924</v>
       </c>
       <c r="R16" t="n">
-        <v>7197575</v>
+        <v>7197844</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2135,32 +2135,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128105203</v>
+        <v>128105181</v>
       </c>
       <c r="B17" t="n">
-        <v>79032</v>
+        <v>80217</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2170,10 +2170,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>742924</v>
+        <v>742967</v>
       </c>
       <c r="R17" t="n">
-        <v>7197844</v>
+        <v>7197575</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2235,7 +2235,7 @@
         <v>128105201</v>
       </c>
       <c r="B18" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2332,7 +2332,7 @@
         <v>128105196</v>
       </c>
       <c r="B19" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2429,7 +2429,7 @@
         <v>128105207</v>
       </c>
       <c r="B20" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2531,7 +2531,7 @@
         <v>128105200</v>
       </c>
       <c r="B21" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2628,7 +2628,7 @@
         <v>128105180</v>
       </c>
       <c r="B22" t="n">
-        <v>57833</v>
+        <v>57845</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2725,7 +2725,7 @@
         <v>128105204</v>
       </c>
       <c r="B23" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2822,7 +2822,7 @@
         <v>128105208</v>
       </c>
       <c r="B24" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2916,32 +2916,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128105187</v>
+        <v>128105197</v>
       </c>
       <c r="B25" t="n">
-        <v>98478</v>
+        <v>79083</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2951,10 +2951,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>742851</v>
+        <v>742882</v>
       </c>
       <c r="R25" t="n">
-        <v>7197885</v>
+        <v>7197625</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3013,10 +3013,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128105189</v>
+        <v>128105187</v>
       </c>
       <c r="B26" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3048,10 +3048,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>742836</v>
+        <v>742851</v>
       </c>
       <c r="R26" t="n">
-        <v>7197877</v>
+        <v>7197885</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3110,32 +3110,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128105197</v>
+        <v>128105189</v>
       </c>
       <c r="B27" t="n">
-        <v>79032</v>
+        <v>98571</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3145,10 +3145,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>742882</v>
+        <v>742836</v>
       </c>
       <c r="R27" t="n">
-        <v>7197625</v>
+        <v>7197877</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3210,7 +3210,7 @@
         <v>128105209</v>
       </c>
       <c r="B28" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
         <v>128105184</v>
       </c>
       <c r="B29" t="n">
-        <v>80135</v>
+        <v>80188</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 40423-2025 artfynd.xlsx
+++ b/artfynd/A 40423-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128105199</v>
+        <v>128105195</v>
       </c>
       <c r="B2" t="n">
-        <v>79083</v>
+        <v>91470</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>743059</v>
+        <v>742779</v>
       </c>
       <c r="R2" t="n">
-        <v>7197601</v>
+        <v>7197609</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-08-28</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128105195</v>
+        <v>128105178</v>
       </c>
       <c r="B3" t="n">
-        <v>91470</v>
+        <v>91452</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>742779</v>
+        <v>743047</v>
       </c>
       <c r="R3" t="n">
-        <v>7197609</v>
+        <v>7197522</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -874,7 +869,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128105178</v>
+        <v>128105177</v>
       </c>
       <c r="B4" t="n">
         <v>91452</v>
@@ -909,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>743047</v>
+        <v>743033</v>
       </c>
       <c r="R4" t="n">
-        <v>7197522</v>
+        <v>7197526</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -971,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128105177</v>
+        <v>128105199</v>
       </c>
       <c r="B5" t="n">
-        <v>91452</v>
+        <v>79083</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -982,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>743033</v>
+        <v>743059</v>
       </c>
       <c r="R5" t="n">
-        <v>7197526</v>
+        <v>7197601</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1042,6 +1037,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1165,32 +1165,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128105176</v>
+        <v>128105191</v>
       </c>
       <c r="B7" t="n">
-        <v>91452</v>
+        <v>98571</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1200,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>742883</v>
+        <v>742729</v>
       </c>
       <c r="R7" t="n">
-        <v>7197635</v>
+        <v>7197803</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1262,32 +1262,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128105205</v>
+        <v>128105183</v>
       </c>
       <c r="B8" t="n">
-        <v>79083</v>
+        <v>98592</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>742831</v>
+        <v>742778</v>
       </c>
       <c r="R8" t="n">
-        <v>7197554</v>
+        <v>7197616</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1359,32 +1359,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128105191</v>
+        <v>128105205</v>
       </c>
       <c r="B9" t="n">
-        <v>98571</v>
+        <v>79083</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1394,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>742729</v>
+        <v>742831</v>
       </c>
       <c r="R9" t="n">
-        <v>7197803</v>
+        <v>7197554</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1456,32 +1456,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128105183</v>
+        <v>128105176</v>
       </c>
       <c r="B10" t="n">
-        <v>98592</v>
+        <v>91452</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221952</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1491,10 +1491,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>742778</v>
+        <v>742883</v>
       </c>
       <c r="R10" t="n">
-        <v>7197616</v>
+        <v>7197635</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1844,7 +1844,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128105206</v>
+        <v>128105202</v>
       </c>
       <c r="B14" t="n">
         <v>79083</v>
@@ -1879,10 +1879,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>743042</v>
+        <v>742977</v>
       </c>
       <c r="R14" t="n">
-        <v>7197583</v>
+        <v>7197813</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1941,7 +1941,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128105202</v>
+        <v>128105206</v>
       </c>
       <c r="B15" t="n">
         <v>79083</v>
@@ -1976,10 +1976,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>742977</v>
+        <v>743042</v>
       </c>
       <c r="R15" t="n">
-        <v>7197813</v>
+        <v>7197583</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2426,7 +2426,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128105207</v>
+        <v>128105200</v>
       </c>
       <c r="B20" t="n">
         <v>79083</v>
@@ -2461,10 +2461,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>743058</v>
+        <v>743052</v>
       </c>
       <c r="R20" t="n">
-        <v>7197514</v>
+        <v>7197729</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2497,11 +2497,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-08-28</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2528,7 +2523,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128105200</v>
+        <v>128105207</v>
       </c>
       <c r="B21" t="n">
         <v>79083</v>
@@ -2563,10 +2558,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>743052</v>
+        <v>743058</v>
       </c>
       <c r="R21" t="n">
-        <v>7197729</v>
+        <v>7197514</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2599,6 +2594,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 40423-2025 artfynd.xlsx
+++ b/artfynd/A 40423-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128105195</v>
+        <v>128105199</v>
       </c>
       <c r="B2" t="n">
-        <v>91470</v>
+        <v>79083</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>742779</v>
+        <v>743059</v>
       </c>
       <c r="R2" t="n">
-        <v>7197609</v>
+        <v>7197601</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,6 +746,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128105178</v>
+        <v>128105195</v>
       </c>
       <c r="B3" t="n">
-        <v>91452</v>
+        <v>91470</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>743047</v>
+        <v>742779</v>
       </c>
       <c r="R3" t="n">
-        <v>7197522</v>
+        <v>7197609</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,7 +874,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128105177</v>
+        <v>128105178</v>
       </c>
       <c r="B4" t="n">
         <v>91452</v>
@@ -904,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>743033</v>
+        <v>743047</v>
       </c>
       <c r="R4" t="n">
-        <v>7197526</v>
+        <v>7197522</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128105199</v>
+        <v>128105177</v>
       </c>
       <c r="B5" t="n">
-        <v>79083</v>
+        <v>91452</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +982,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>743059</v>
+        <v>743033</v>
       </c>
       <c r="R5" t="n">
-        <v>7197601</v>
+        <v>7197526</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1037,11 +1042,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-28</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1165,32 +1165,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128105191</v>
+        <v>128105205</v>
       </c>
       <c r="B7" t="n">
-        <v>98571</v>
+        <v>79083</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1200,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>742729</v>
+        <v>742831</v>
       </c>
       <c r="R7" t="n">
-        <v>7197803</v>
+        <v>7197554</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1262,32 +1262,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128105183</v>
+        <v>128105176</v>
       </c>
       <c r="B8" t="n">
-        <v>98592</v>
+        <v>91452</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221952</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>742778</v>
+        <v>742883</v>
       </c>
       <c r="R8" t="n">
-        <v>7197616</v>
+        <v>7197635</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1359,32 +1359,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128105205</v>
+        <v>128105183</v>
       </c>
       <c r="B9" t="n">
-        <v>79083</v>
+        <v>98592</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1394,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>742831</v>
+        <v>742778</v>
       </c>
       <c r="R9" t="n">
-        <v>7197554</v>
+        <v>7197616</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1456,32 +1456,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128105176</v>
+        <v>128105191</v>
       </c>
       <c r="B10" t="n">
-        <v>91452</v>
+        <v>98571</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1491,10 +1491,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>742883</v>
+        <v>742729</v>
       </c>
       <c r="R10" t="n">
-        <v>7197635</v>
+        <v>7197803</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1553,32 +1553,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128105198</v>
+        <v>128105193</v>
       </c>
       <c r="B11" t="n">
-        <v>79083</v>
+        <v>98571</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1588,10 +1588,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>743076</v>
+        <v>742919</v>
       </c>
       <c r="R11" t="n">
-        <v>7197586</v>
+        <v>7197599</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1650,7 +1650,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128105193</v>
+        <v>128105190</v>
       </c>
       <c r="B12" t="n">
         <v>98571</v>
@@ -1685,10 +1685,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>742919</v>
+        <v>743078</v>
       </c>
       <c r="R12" t="n">
-        <v>7197599</v>
+        <v>7197587</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1747,32 +1747,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128105190</v>
+        <v>128105198</v>
       </c>
       <c r="B13" t="n">
-        <v>98571</v>
+        <v>79083</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>743078</v>
+        <v>743076</v>
       </c>
       <c r="R13" t="n">
-        <v>7197587</v>
+        <v>7197586</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1844,7 +1844,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128105202</v>
+        <v>128105206</v>
       </c>
       <c r="B14" t="n">
         <v>79083</v>
@@ -1879,10 +1879,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>742977</v>
+        <v>743042</v>
       </c>
       <c r="R14" t="n">
-        <v>7197813</v>
+        <v>7197583</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1941,7 +1941,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128105206</v>
+        <v>128105202</v>
       </c>
       <c r="B15" t="n">
         <v>79083</v>
@@ -1976,10 +1976,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>743042</v>
+        <v>742977</v>
       </c>
       <c r="R15" t="n">
-        <v>7197583</v>
+        <v>7197813</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2038,32 +2038,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128105203</v>
+        <v>128105181</v>
       </c>
       <c r="B16" t="n">
-        <v>79083</v>
+        <v>80217</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2073,10 +2073,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>742924</v>
+        <v>742967</v>
       </c>
       <c r="R16" t="n">
-        <v>7197844</v>
+        <v>7197575</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2135,32 +2135,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128105181</v>
+        <v>128105203</v>
       </c>
       <c r="B17" t="n">
-        <v>80217</v>
+        <v>79083</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2170,10 +2170,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>742967</v>
+        <v>742924</v>
       </c>
       <c r="R17" t="n">
-        <v>7197575</v>
+        <v>7197844</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2426,7 +2426,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128105200</v>
+        <v>128105207</v>
       </c>
       <c r="B20" t="n">
         <v>79083</v>
@@ -2461,10 +2461,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>743052</v>
+        <v>743058</v>
       </c>
       <c r="R20" t="n">
-        <v>7197729</v>
+        <v>7197514</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2497,6 +2497,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2523,7 +2528,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128105207</v>
+        <v>128105200</v>
       </c>
       <c r="B21" t="n">
         <v>79083</v>
@@ -2558,10 +2563,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>743058</v>
+        <v>743052</v>
       </c>
       <c r="R21" t="n">
-        <v>7197514</v>
+        <v>7197729</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2594,11 +2599,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-08-28</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2916,32 +2916,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128105197</v>
+        <v>128105187</v>
       </c>
       <c r="B25" t="n">
-        <v>79083</v>
+        <v>98571</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2951,10 +2951,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>742882</v>
+        <v>742851</v>
       </c>
       <c r="R25" t="n">
-        <v>7197625</v>
+        <v>7197885</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3013,7 +3013,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128105187</v>
+        <v>128105189</v>
       </c>
       <c r="B26" t="n">
         <v>98571</v>
@@ -3048,10 +3048,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>742851</v>
+        <v>742836</v>
       </c>
       <c r="R26" t="n">
-        <v>7197885</v>
+        <v>7197877</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3110,32 +3110,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128105189</v>
+        <v>128105197</v>
       </c>
       <c r="B27" t="n">
-        <v>98571</v>
+        <v>79083</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3145,10 +3145,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>742836</v>
+        <v>742882</v>
       </c>
       <c r="R27" t="n">
-        <v>7197877</v>
+        <v>7197625</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>

--- a/artfynd/A 40423-2025 artfynd.xlsx
+++ b/artfynd/A 40423-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128105199</v>
+        <v>128105177</v>
       </c>
       <c r="B2" t="n">
-        <v>79083</v>
+        <v>91452</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>743059</v>
+        <v>743033</v>
       </c>
       <c r="R2" t="n">
-        <v>7197601</v>
+        <v>7197526</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-08-28</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128105195</v>
+        <v>128105199</v>
       </c>
       <c r="B3" t="n">
-        <v>91470</v>
+        <v>79083</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>742779</v>
+        <v>743059</v>
       </c>
       <c r="R3" t="n">
-        <v>7197609</v>
+        <v>7197601</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -848,6 +843,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -874,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128105178</v>
+        <v>128105195</v>
       </c>
       <c r="B4" t="n">
-        <v>91452</v>
+        <v>91470</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,21 +885,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>743047</v>
+        <v>742779</v>
       </c>
       <c r="R4" t="n">
-        <v>7197522</v>
+        <v>7197609</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -971,7 +971,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128105177</v>
+        <v>128105178</v>
       </c>
       <c r="B5" t="n">
         <v>91452</v>
@@ -1006,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>743033</v>
+        <v>743047</v>
       </c>
       <c r="R5" t="n">
-        <v>7197526</v>
+        <v>7197522</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 40423-2025 artfynd.xlsx
+++ b/artfynd/A 40423-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128105177</v>
+        <v>128105178</v>
       </c>
       <c r="B2" t="n">
-        <v>91452</v>
+        <v>91464</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>743033</v>
+        <v>743047</v>
       </c>
       <c r="R2" t="n">
-        <v>7197526</v>
+        <v>7197522</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128105199</v>
+        <v>128105177</v>
       </c>
       <c r="B3" t="n">
-        <v>79083</v>
+        <v>91464</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>743059</v>
+        <v>743033</v>
       </c>
       <c r="R3" t="n">
-        <v>7197601</v>
+        <v>7197526</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -843,11 +843,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-28</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,7 +872,7 @@
         <v>128105195</v>
       </c>
       <c r="B4" t="n">
-        <v>91470</v>
+        <v>91482</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -971,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128105178</v>
+        <v>128105199</v>
       </c>
       <c r="B5" t="n">
-        <v>91452</v>
+        <v>79087</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -982,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>743047</v>
+        <v>743059</v>
       </c>
       <c r="R5" t="n">
-        <v>7197522</v>
+        <v>7197601</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1042,6 +1037,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1071,7 +1071,7 @@
         <v>128105182</v>
       </c>
       <c r="B6" t="n">
-        <v>98592</v>
+        <v>98606</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         <v>128105205</v>
       </c>
       <c r="B7" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>128105176</v>
       </c>
       <c r="B8" t="n">
-        <v>91452</v>
+        <v>91464</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1359,32 +1359,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128105183</v>
+        <v>128105191</v>
       </c>
       <c r="B9" t="n">
-        <v>98592</v>
+        <v>98585</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1394,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>742778</v>
+        <v>742729</v>
       </c>
       <c r="R9" t="n">
-        <v>7197616</v>
+        <v>7197803</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1456,32 +1456,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128105191</v>
+        <v>128105183</v>
       </c>
       <c r="B10" t="n">
-        <v>98571</v>
+        <v>98606</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1491,10 +1491,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>742729</v>
+        <v>742778</v>
       </c>
       <c r="R10" t="n">
-        <v>7197803</v>
+        <v>7197616</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1556,7 +1556,7 @@
         <v>128105193</v>
       </c>
       <c r="B11" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1653,7 +1653,7 @@
         <v>128105190</v>
       </c>
       <c r="B12" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
         <v>128105198</v>
       </c>
       <c r="B13" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1844,10 +1844,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128105206</v>
+        <v>128105202</v>
       </c>
       <c r="B14" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1879,10 +1879,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>743042</v>
+        <v>742977</v>
       </c>
       <c r="R14" t="n">
-        <v>7197583</v>
+        <v>7197813</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1941,10 +1941,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128105202</v>
+        <v>128105206</v>
       </c>
       <c r="B15" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1976,10 +1976,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>742977</v>
+        <v>743042</v>
       </c>
       <c r="R15" t="n">
-        <v>7197813</v>
+        <v>7197583</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2038,32 +2038,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128105181</v>
+        <v>128105203</v>
       </c>
       <c r="B16" t="n">
-        <v>80217</v>
+        <v>79087</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2073,10 +2073,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>742967</v>
+        <v>742924</v>
       </c>
       <c r="R16" t="n">
-        <v>7197575</v>
+        <v>7197844</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2135,32 +2135,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128105203</v>
+        <v>128105181</v>
       </c>
       <c r="B17" t="n">
-        <v>79083</v>
+        <v>80221</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2170,10 +2170,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>742924</v>
+        <v>742967</v>
       </c>
       <c r="R17" t="n">
-        <v>7197844</v>
+        <v>7197575</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2235,7 +2235,7 @@
         <v>128105201</v>
       </c>
       <c r="B18" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2332,7 +2332,7 @@
         <v>128105196</v>
       </c>
       <c r="B19" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2429,7 +2429,7 @@
         <v>128105207</v>
       </c>
       <c r="B20" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2531,7 +2531,7 @@
         <v>128105200</v>
       </c>
       <c r="B21" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2628,7 +2628,7 @@
         <v>128105180</v>
       </c>
       <c r="B22" t="n">
-        <v>57845</v>
+        <v>57849</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2725,7 +2725,7 @@
         <v>128105204</v>
       </c>
       <c r="B23" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2822,7 +2822,7 @@
         <v>128105208</v>
       </c>
       <c r="B24" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2916,32 +2916,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128105187</v>
+        <v>128105197</v>
       </c>
       <c r="B25" t="n">
-        <v>98571</v>
+        <v>79087</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2951,10 +2951,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>742851</v>
+        <v>742882</v>
       </c>
       <c r="R25" t="n">
-        <v>7197885</v>
+        <v>7197625</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3013,10 +3013,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128105189</v>
+        <v>128105187</v>
       </c>
       <c r="B26" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3048,10 +3048,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>742836</v>
+        <v>742851</v>
       </c>
       <c r="R26" t="n">
-        <v>7197877</v>
+        <v>7197885</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3110,32 +3110,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128105197</v>
+        <v>128105189</v>
       </c>
       <c r="B27" t="n">
-        <v>79083</v>
+        <v>98585</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3145,10 +3145,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>742882</v>
+        <v>742836</v>
       </c>
       <c r="R27" t="n">
-        <v>7197625</v>
+        <v>7197877</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3210,7 +3210,7 @@
         <v>128105209</v>
       </c>
       <c r="B28" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
         <v>128105184</v>
       </c>
       <c r="B29" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 40423-2025 artfynd.xlsx
+++ b/artfynd/A 40423-2025 artfynd.xlsx
@@ -1165,10 +1165,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128105205</v>
+        <v>128105176</v>
       </c>
       <c r="B7" t="n">
-        <v>79087</v>
+        <v>91464</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1176,21 +1176,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1200,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>742831</v>
+        <v>742883</v>
       </c>
       <c r="R7" t="n">
-        <v>7197554</v>
+        <v>7197635</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1262,10 +1262,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128105176</v>
+        <v>128105205</v>
       </c>
       <c r="B8" t="n">
-        <v>91464</v>
+        <v>79087</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1273,21 +1273,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>742883</v>
+        <v>742831</v>
       </c>
       <c r="R8" t="n">
-        <v>7197635</v>
+        <v>7197554</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -2038,32 +2038,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128105203</v>
+        <v>128105181</v>
       </c>
       <c r="B16" t="n">
-        <v>79087</v>
+        <v>80221</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2073,10 +2073,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>742924</v>
+        <v>742967</v>
       </c>
       <c r="R16" t="n">
-        <v>7197844</v>
+        <v>7197575</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2135,32 +2135,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128105181</v>
+        <v>128105203</v>
       </c>
       <c r="B17" t="n">
-        <v>80221</v>
+        <v>79087</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2170,10 +2170,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>742967</v>
+        <v>742924</v>
       </c>
       <c r="R17" t="n">
-        <v>7197575</v>
+        <v>7197844</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>

--- a/artfynd/A 40423-2025 artfynd.xlsx
+++ b/artfynd/A 40423-2025 artfynd.xlsx
@@ -1165,32 +1165,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128105176</v>
+        <v>128105191</v>
       </c>
       <c r="B7" t="n">
-        <v>91464</v>
+        <v>98585</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1200,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>742883</v>
+        <v>742729</v>
       </c>
       <c r="R7" t="n">
-        <v>7197635</v>
+        <v>7197803</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1262,32 +1262,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128105205</v>
+        <v>128105183</v>
       </c>
       <c r="B8" t="n">
-        <v>79087</v>
+        <v>98606</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>742831</v>
+        <v>742778</v>
       </c>
       <c r="R8" t="n">
-        <v>7197554</v>
+        <v>7197616</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1359,32 +1359,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128105191</v>
+        <v>128105176</v>
       </c>
       <c r="B9" t="n">
-        <v>98585</v>
+        <v>91464</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1394,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>742729</v>
+        <v>742883</v>
       </c>
       <c r="R9" t="n">
-        <v>7197803</v>
+        <v>7197635</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1456,32 +1456,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128105183</v>
+        <v>128105205</v>
       </c>
       <c r="B10" t="n">
-        <v>98606</v>
+        <v>79087</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1491,10 +1491,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>742778</v>
+        <v>742831</v>
       </c>
       <c r="R10" t="n">
-        <v>7197616</v>
+        <v>7197554</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1553,32 +1553,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128105193</v>
+        <v>128105198</v>
       </c>
       <c r="B11" t="n">
-        <v>98585</v>
+        <v>79087</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1588,10 +1588,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>742919</v>
+        <v>743076</v>
       </c>
       <c r="R11" t="n">
-        <v>7197599</v>
+        <v>7197586</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1650,7 +1650,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128105190</v>
+        <v>128105193</v>
       </c>
       <c r="B12" t="n">
         <v>98585</v>
@@ -1685,10 +1685,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>743078</v>
+        <v>742919</v>
       </c>
       <c r="R12" t="n">
-        <v>7197587</v>
+        <v>7197599</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1747,32 +1747,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128105198</v>
+        <v>128105190</v>
       </c>
       <c r="B13" t="n">
-        <v>79087</v>
+        <v>98585</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>743076</v>
+        <v>743078</v>
       </c>
       <c r="R13" t="n">
-        <v>7197586</v>
+        <v>7197587</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2038,32 +2038,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128105181</v>
+        <v>128105203</v>
       </c>
       <c r="B16" t="n">
-        <v>80221</v>
+        <v>79087</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2073,10 +2073,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>742967</v>
+        <v>742924</v>
       </c>
       <c r="R16" t="n">
-        <v>7197575</v>
+        <v>7197844</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2135,32 +2135,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128105203</v>
+        <v>128105181</v>
       </c>
       <c r="B17" t="n">
-        <v>79087</v>
+        <v>80221</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2170,10 +2170,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>742924</v>
+        <v>742967</v>
       </c>
       <c r="R17" t="n">
-        <v>7197844</v>
+        <v>7197575</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>

--- a/artfynd/A 40423-2025 artfynd.xlsx
+++ b/artfynd/A 40423-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128105178</v>
+        <v>128105199</v>
       </c>
       <c r="B2" t="n">
-        <v>91464</v>
+        <v>79089</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>743047</v>
+        <v>743059</v>
       </c>
       <c r="R2" t="n">
-        <v>7197522</v>
+        <v>7197601</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,6 +746,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128105177</v>
+        <v>128105178</v>
       </c>
       <c r="B3" t="n">
-        <v>91464</v>
+        <v>91466</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>743033</v>
+        <v>743047</v>
       </c>
       <c r="R3" t="n">
-        <v>7197526</v>
+        <v>7197522</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128105195</v>
+        <v>128105177</v>
       </c>
       <c r="B4" t="n">
-        <v>91482</v>
+        <v>91466</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +885,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>742779</v>
+        <v>743033</v>
       </c>
       <c r="R4" t="n">
-        <v>7197609</v>
+        <v>7197526</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128105199</v>
+        <v>128105195</v>
       </c>
       <c r="B5" t="n">
-        <v>79087</v>
+        <v>91484</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +982,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>743059</v>
+        <v>742779</v>
       </c>
       <c r="R5" t="n">
-        <v>7197601</v>
+        <v>7197609</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1037,11 +1042,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-28</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1071,7 +1071,7 @@
         <v>128105182</v>
       </c>
       <c r="B6" t="n">
-        <v>98606</v>
+        <v>98612</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1165,32 +1165,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128105191</v>
+        <v>128105205</v>
       </c>
       <c r="B7" t="n">
-        <v>98585</v>
+        <v>79089</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1200,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>742729</v>
+        <v>742831</v>
       </c>
       <c r="R7" t="n">
-        <v>7197803</v>
+        <v>7197554</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1262,32 +1262,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128105183</v>
+        <v>128105191</v>
       </c>
       <c r="B8" t="n">
-        <v>98606</v>
+        <v>98591</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>742778</v>
+        <v>742729</v>
       </c>
       <c r="R8" t="n">
-        <v>7197616</v>
+        <v>7197803</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1359,32 +1359,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128105176</v>
+        <v>128105183</v>
       </c>
       <c r="B9" t="n">
-        <v>91464</v>
+        <v>98612</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>221952</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1394,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>742883</v>
+        <v>742778</v>
       </c>
       <c r="R9" t="n">
-        <v>7197635</v>
+        <v>7197616</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1456,10 +1456,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128105205</v>
+        <v>128105176</v>
       </c>
       <c r="B10" t="n">
-        <v>79087</v>
+        <v>91466</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1467,21 +1467,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1491,10 +1491,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>742831</v>
+        <v>742883</v>
       </c>
       <c r="R10" t="n">
-        <v>7197554</v>
+        <v>7197635</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1556,7 +1556,7 @@
         <v>128105198</v>
       </c>
       <c r="B11" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1653,7 +1653,7 @@
         <v>128105193</v>
       </c>
       <c r="B12" t="n">
-        <v>98585</v>
+        <v>98591</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
         <v>128105190</v>
       </c>
       <c r="B13" t="n">
-        <v>98585</v>
+        <v>98591</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1844,10 +1844,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128105202</v>
+        <v>128105206</v>
       </c>
       <c r="B14" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1879,10 +1879,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>742977</v>
+        <v>743042</v>
       </c>
       <c r="R14" t="n">
-        <v>7197813</v>
+        <v>7197583</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1941,10 +1941,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128105206</v>
+        <v>128105202</v>
       </c>
       <c r="B15" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1976,10 +1976,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>743042</v>
+        <v>742977</v>
       </c>
       <c r="R15" t="n">
-        <v>7197583</v>
+        <v>7197813</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2038,32 +2038,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128105203</v>
+        <v>128105181</v>
       </c>
       <c r="B16" t="n">
-        <v>79087</v>
+        <v>80223</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2073,10 +2073,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>742924</v>
+        <v>742967</v>
       </c>
       <c r="R16" t="n">
-        <v>7197844</v>
+        <v>7197575</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2135,32 +2135,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128105181</v>
+        <v>128105203</v>
       </c>
       <c r="B17" t="n">
-        <v>80221</v>
+        <v>79089</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2170,10 +2170,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>742967</v>
+        <v>742924</v>
       </c>
       <c r="R17" t="n">
-        <v>7197575</v>
+        <v>7197844</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2235,7 +2235,7 @@
         <v>128105201</v>
       </c>
       <c r="B18" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2332,7 +2332,7 @@
         <v>128105196</v>
       </c>
       <c r="B19" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2429,7 +2429,7 @@
         <v>128105207</v>
       </c>
       <c r="B20" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2531,7 +2531,7 @@
         <v>128105200</v>
       </c>
       <c r="B21" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2725,7 +2725,7 @@
         <v>128105204</v>
       </c>
       <c r="B23" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2822,7 +2822,7 @@
         <v>128105208</v>
       </c>
       <c r="B24" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2919,7 +2919,7 @@
         <v>128105197</v>
       </c>
       <c r="B25" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3016,7 +3016,7 @@
         <v>128105187</v>
       </c>
       <c r="B26" t="n">
-        <v>98585</v>
+        <v>98591</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3113,7 +3113,7 @@
         <v>128105189</v>
       </c>
       <c r="B27" t="n">
-        <v>98585</v>
+        <v>98591</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3210,7 +3210,7 @@
         <v>128105209</v>
       </c>
       <c r="B28" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
         <v>128105184</v>
       </c>
       <c r="B29" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 40423-2025 artfynd.xlsx
+++ b/artfynd/A 40423-2025 artfynd.xlsx
@@ -1262,32 +1262,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128105191</v>
+        <v>128105183</v>
       </c>
       <c r="B8" t="n">
-        <v>98591</v>
+        <v>98612</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>742729</v>
+        <v>742778</v>
       </c>
       <c r="R8" t="n">
-        <v>7197803</v>
+        <v>7197616</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1359,32 +1359,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128105183</v>
+        <v>128105191</v>
       </c>
       <c r="B9" t="n">
-        <v>98612</v>
+        <v>98591</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1394,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>742778</v>
+        <v>742729</v>
       </c>
       <c r="R9" t="n">
-        <v>7197616</v>
+        <v>7197803</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1553,32 +1553,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128105198</v>
+        <v>128105193</v>
       </c>
       <c r="B11" t="n">
-        <v>79089</v>
+        <v>98591</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1588,10 +1588,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>743076</v>
+        <v>742919</v>
       </c>
       <c r="R11" t="n">
-        <v>7197586</v>
+        <v>7197599</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1650,7 +1650,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128105193</v>
+        <v>128105190</v>
       </c>
       <c r="B12" t="n">
         <v>98591</v>
@@ -1685,10 +1685,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>742919</v>
+        <v>743078</v>
       </c>
       <c r="R12" t="n">
-        <v>7197599</v>
+        <v>7197587</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1747,32 +1747,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128105190</v>
+        <v>128105198</v>
       </c>
       <c r="B13" t="n">
-        <v>98591</v>
+        <v>79089</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>743078</v>
+        <v>743076</v>
       </c>
       <c r="R13" t="n">
-        <v>7197587</v>
+        <v>7197586</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 40423-2025 artfynd.xlsx
+++ b/artfynd/A 40423-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128105199</v>
       </c>
       <c r="B2" t="n">
-        <v>79089</v>
+        <v>79120</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -773,14 +773,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
         <v>128105178</v>
       </c>
       <c r="B3" t="n">
-        <v>91466</v>
+        <v>91504</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -870,14 +874,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
         <v>128105177</v>
       </c>
       <c r="B4" t="n">
-        <v>91466</v>
+        <v>91504</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -967,14 +975,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr"/>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
         <v>128105195</v>
       </c>
       <c r="B5" t="n">
-        <v>91484</v>
+        <v>91522</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1064,14 +1076,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr"/>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
         <v>128105182</v>
       </c>
       <c r="B6" t="n">
-        <v>98612</v>
+        <v>98653</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1161,14 +1177,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY6" t="inlineStr"/>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
         <v>128105205</v>
       </c>
       <c r="B7" t="n">
-        <v>79089</v>
+        <v>79120</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1258,14 +1278,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY7" t="inlineStr"/>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
         <v>128105183</v>
       </c>
       <c r="B8" t="n">
-        <v>98612</v>
+        <v>98653</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1355,14 +1379,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY8" t="inlineStr"/>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
         <v>128105191</v>
       </c>
       <c r="B9" t="n">
-        <v>98591</v>
+        <v>98632</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1452,14 +1480,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY9" t="inlineStr"/>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
         <v>128105176</v>
       </c>
       <c r="B10" t="n">
-        <v>91466</v>
+        <v>91504</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1549,14 +1581,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY10" t="inlineStr"/>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
         <v>128105193</v>
       </c>
       <c r="B11" t="n">
-        <v>98591</v>
+        <v>98632</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1646,14 +1682,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY11" t="inlineStr"/>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
         <v>128105190</v>
       </c>
       <c r="B12" t="n">
-        <v>98591</v>
+        <v>98632</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1743,14 +1783,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY12" t="inlineStr"/>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
         <v>128105198</v>
       </c>
       <c r="B13" t="n">
-        <v>79089</v>
+        <v>79120</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1840,14 +1884,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY13" t="inlineStr"/>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
         <v>128105206</v>
       </c>
       <c r="B14" t="n">
-        <v>79089</v>
+        <v>79120</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1937,14 +1985,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY14" t="inlineStr"/>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
         <v>128105202</v>
       </c>
       <c r="B15" t="n">
-        <v>79089</v>
+        <v>79120</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2034,14 +2086,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY15" t="inlineStr"/>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
         <v>128105181</v>
       </c>
       <c r="B16" t="n">
-        <v>80223</v>
+        <v>80254</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2131,14 +2187,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY16" t="inlineStr"/>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
         <v>128105203</v>
       </c>
       <c r="B17" t="n">
-        <v>79089</v>
+        <v>79120</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2228,14 +2288,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY17" t="inlineStr"/>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
         <v>128105201</v>
       </c>
       <c r="B18" t="n">
-        <v>79089</v>
+        <v>79120</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2325,14 +2389,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY18" t="inlineStr"/>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
         <v>128105196</v>
       </c>
       <c r="B19" t="n">
-        <v>79089</v>
+        <v>79120</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2422,14 +2490,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY19" t="inlineStr"/>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
         <v>128105207</v>
       </c>
       <c r="B20" t="n">
-        <v>79089</v>
+        <v>79120</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2524,14 +2596,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY20" t="inlineStr"/>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
         <v>128105200</v>
       </c>
       <c r="B21" t="n">
-        <v>79089</v>
+        <v>79120</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2621,14 +2697,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY21" t="inlineStr"/>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
         <v>128105180</v>
       </c>
       <c r="B22" t="n">
-        <v>57849</v>
+        <v>57876</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2718,14 +2798,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY22" t="inlineStr"/>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
         <v>128105204</v>
       </c>
       <c r="B23" t="n">
-        <v>79089</v>
+        <v>79120</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2815,14 +2899,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY23" t="inlineStr"/>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
         <v>128105208</v>
       </c>
       <c r="B24" t="n">
-        <v>79089</v>
+        <v>79120</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2912,14 +3000,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY24" t="inlineStr"/>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
         <v>128105197</v>
       </c>
       <c r="B25" t="n">
-        <v>79089</v>
+        <v>79120</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3009,14 +3101,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY25" t="inlineStr"/>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
         <v>128105187</v>
       </c>
       <c r="B26" t="n">
-        <v>98591</v>
+        <v>98632</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3106,14 +3202,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY26" t="inlineStr"/>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
         <v>128105189</v>
       </c>
       <c r="B27" t="n">
-        <v>98591</v>
+        <v>98632</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3203,14 +3303,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY27" t="inlineStr"/>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
         <v>128105209</v>
       </c>
       <c r="B28" t="n">
-        <v>79089</v>
+        <v>79120</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3300,14 +3404,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY28" t="inlineStr"/>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
         <v>128105184</v>
       </c>
       <c r="B29" t="n">
-        <v>80194</v>
+        <v>80225</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3397,7 +3505,11 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY29" t="inlineStr"/>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 40423-2025 artfynd.xlsx
+++ b/artfynd/A 40423-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128105199</v>
       </c>
       <c r="B2" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>128105178</v>
       </c>
       <c r="B3" t="n">
-        <v>91504</v>
+        <v>91508</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
         <v>128105177</v>
       </c>
       <c r="B4" t="n">
-        <v>91504</v>
+        <v>91508</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -986,7 +986,7 @@
         <v>128105195</v>
       </c>
       <c r="B5" t="n">
-        <v>91522</v>
+        <v>91526</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
         <v>128105182</v>
       </c>
       <c r="B6" t="n">
-        <v>98653</v>
+        <v>98657</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>128105205</v>
       </c>
       <c r="B7" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1289,7 +1289,7 @@
         <v>128105183</v>
       </c>
       <c r="B8" t="n">
-        <v>98653</v>
+        <v>98657</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1390,7 +1390,7 @@
         <v>128105191</v>
       </c>
       <c r="B9" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>128105176</v>
       </c>
       <c r="B10" t="n">
-        <v>91504</v>
+        <v>91508</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1592,7 +1592,7 @@
         <v>128105193</v>
       </c>
       <c r="B11" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>128105190</v>
       </c>
       <c r="B12" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         <v>128105198</v>
       </c>
       <c r="B13" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1895,7 +1895,7 @@
         <v>128105206</v>
       </c>
       <c r="B14" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1996,7 +1996,7 @@
         <v>128105202</v>
       </c>
       <c r="B15" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
         <v>128105181</v>
       </c>
       <c r="B16" t="n">
-        <v>80254</v>
+        <v>80258</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2198,7 +2198,7 @@
         <v>128105203</v>
       </c>
       <c r="B17" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2299,7 +2299,7 @@
         <v>128105201</v>
       </c>
       <c r="B18" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2400,7 +2400,7 @@
         <v>128105196</v>
       </c>
       <c r="B19" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2501,7 +2501,7 @@
         <v>128105207</v>
       </c>
       <c r="B20" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2607,7 +2607,7 @@
         <v>128105200</v>
       </c>
       <c r="B21" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2708,7 +2708,7 @@
         <v>128105180</v>
       </c>
       <c r="B22" t="n">
-        <v>57876</v>
+        <v>57880</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2809,7 +2809,7 @@
         <v>128105204</v>
       </c>
       <c r="B23" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2910,7 +2910,7 @@
         <v>128105208</v>
       </c>
       <c r="B24" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3011,7 +3011,7 @@
         <v>128105197</v>
       </c>
       <c r="B25" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3112,7 +3112,7 @@
         <v>128105187</v>
       </c>
       <c r="B26" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3213,7 +3213,7 @@
         <v>128105189</v>
       </c>
       <c r="B27" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3314,7 +3314,7 @@
         <v>128105209</v>
       </c>
       <c r="B28" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3415,7 +3415,7 @@
         <v>128105184</v>
       </c>
       <c r="B29" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 40423-2025 artfynd.xlsx
+++ b/artfynd/A 40423-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128105199</v>
       </c>
       <c r="B2" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>128105178</v>
       </c>
       <c r="B3" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
         <v>128105177</v>
       </c>
       <c r="B4" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -986,7 +986,7 @@
         <v>128105195</v>
       </c>
       <c r="B5" t="n">
-        <v>91526</v>
+        <v>91531</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
         <v>128105182</v>
       </c>
       <c r="B6" t="n">
-        <v>98657</v>
+        <v>98664</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>128105205</v>
       </c>
       <c r="B7" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1289,7 +1289,7 @@
         <v>128105183</v>
       </c>
       <c r="B8" t="n">
-        <v>98657</v>
+        <v>98664</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1390,7 +1390,7 @@
         <v>128105191</v>
       </c>
       <c r="B9" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>128105176</v>
       </c>
       <c r="B10" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1592,7 +1592,7 @@
         <v>128105193</v>
       </c>
       <c r="B11" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>128105190</v>
       </c>
       <c r="B12" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         <v>128105198</v>
       </c>
       <c r="B13" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1895,7 +1895,7 @@
         <v>128105206</v>
       </c>
       <c r="B14" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1996,7 +1996,7 @@
         <v>128105202</v>
       </c>
       <c r="B15" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
         <v>128105181</v>
       </c>
       <c r="B16" t="n">
-        <v>80258</v>
+        <v>80163</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2198,7 +2198,7 @@
         <v>128105203</v>
       </c>
       <c r="B17" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2299,7 +2299,7 @@
         <v>128105201</v>
       </c>
       <c r="B18" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2400,7 +2400,7 @@
         <v>128105196</v>
       </c>
       <c r="B19" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2501,7 +2501,7 @@
         <v>128105207</v>
       </c>
       <c r="B20" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2607,7 +2607,7 @@
         <v>128105200</v>
       </c>
       <c r="B21" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2708,7 +2708,7 @@
         <v>128105180</v>
       </c>
       <c r="B22" t="n">
-        <v>57880</v>
+        <v>57883</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2809,7 +2809,7 @@
         <v>128105204</v>
       </c>
       <c r="B23" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2910,7 +2910,7 @@
         <v>128105208</v>
       </c>
       <c r="B24" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3011,7 +3011,7 @@
         <v>128105197</v>
       </c>
       <c r="B25" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3112,7 +3112,7 @@
         <v>128105187</v>
       </c>
       <c r="B26" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3213,7 +3213,7 @@
         <v>128105189</v>
       </c>
       <c r="B27" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3314,7 +3314,7 @@
         <v>128105209</v>
       </c>
       <c r="B28" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3415,7 +3415,7 @@
         <v>128105184</v>
       </c>
       <c r="B29" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 40423-2025 artfynd.xlsx
+++ b/artfynd/A 40423-2025 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>128105178</v>
       </c>
       <c r="B3" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
         <v>128105177</v>
       </c>
       <c r="B4" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -986,7 +986,7 @@
         <v>128105195</v>
       </c>
       <c r="B5" t="n">
-        <v>91538</v>
+        <v>91541</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
         <v>128105182</v>
       </c>
       <c r="B6" t="n">
-        <v>98672</v>
+        <v>98677</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1289,7 +1289,7 @@
         <v>128105183</v>
       </c>
       <c r="B8" t="n">
-        <v>98672</v>
+        <v>98677</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1390,7 +1390,7 @@
         <v>128105191</v>
       </c>
       <c r="B9" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>128105176</v>
       </c>
       <c r="B10" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1592,7 +1592,7 @@
         <v>128105193</v>
       </c>
       <c r="B11" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>128105190</v>
       </c>
       <c r="B12" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -3112,7 +3112,7 @@
         <v>128105187</v>
       </c>
       <c r="B26" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3213,7 +3213,7 @@
         <v>128105189</v>
       </c>
       <c r="B27" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 40423-2025 artfynd.xlsx
+++ b/artfynd/A 40423-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128105199</v>
       </c>
       <c r="B2" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>128105178</v>
       </c>
       <c r="B3" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
         <v>128105177</v>
       </c>
       <c r="B4" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -986,7 +986,7 @@
         <v>128105195</v>
       </c>
       <c r="B5" t="n">
-        <v>91541</v>
+        <v>91544</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
         <v>128105182</v>
       </c>
       <c r="B6" t="n">
-        <v>98677</v>
+        <v>98680</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>128105205</v>
       </c>
       <c r="B7" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1289,7 +1289,7 @@
         <v>128105183</v>
       </c>
       <c r="B8" t="n">
-        <v>98677</v>
+        <v>98680</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1390,7 +1390,7 @@
         <v>128105191</v>
       </c>
       <c r="B9" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>128105176</v>
       </c>
       <c r="B10" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1592,7 +1592,7 @@
         <v>128105193</v>
       </c>
       <c r="B11" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>128105190</v>
       </c>
       <c r="B12" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         <v>128105198</v>
       </c>
       <c r="B13" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1895,7 +1895,7 @@
         <v>128105206</v>
       </c>
       <c r="B14" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1996,7 +1996,7 @@
         <v>128105202</v>
       </c>
       <c r="B15" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
         <v>128105181</v>
       </c>
       <c r="B16" t="n">
-        <v>80168</v>
+        <v>80169</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2198,7 +2198,7 @@
         <v>128105203</v>
       </c>
       <c r="B17" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2299,7 +2299,7 @@
         <v>128105201</v>
       </c>
       <c r="B18" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2400,7 +2400,7 @@
         <v>128105196</v>
       </c>
       <c r="B19" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2501,7 +2501,7 @@
         <v>128105207</v>
       </c>
       <c r="B20" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2607,7 +2607,7 @@
         <v>128105200</v>
       </c>
       <c r="B21" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2809,7 +2809,7 @@
         <v>128105204</v>
       </c>
       <c r="B23" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2910,7 +2910,7 @@
         <v>128105208</v>
       </c>
       <c r="B24" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3011,7 +3011,7 @@
         <v>128105197</v>
       </c>
       <c r="B25" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3112,7 +3112,7 @@
         <v>128105187</v>
       </c>
       <c r="B26" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3213,7 +3213,7 @@
         <v>128105189</v>
       </c>
       <c r="B27" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3314,7 +3314,7 @@
         <v>128105209</v>
       </c>
       <c r="B28" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3415,7 +3415,7 @@
         <v>128105184</v>
       </c>
       <c r="B29" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 40423-2025 artfynd.xlsx
+++ b/artfynd/A 40423-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128105199</v>
       </c>
       <c r="B2" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>128105178</v>
       </c>
       <c r="B3" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
         <v>128105177</v>
       </c>
       <c r="B4" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -986,7 +986,7 @@
         <v>128105195</v>
       </c>
       <c r="B5" t="n">
-        <v>91544</v>
+        <v>91551</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
         <v>128105182</v>
       </c>
       <c r="B6" t="n">
-        <v>98680</v>
+        <v>98690</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>128105205</v>
       </c>
       <c r="B7" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1289,7 +1289,7 @@
         <v>128105183</v>
       </c>
       <c r="B8" t="n">
-        <v>98680</v>
+        <v>98690</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1390,7 +1390,7 @@
         <v>128105191</v>
       </c>
       <c r="B9" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>128105176</v>
       </c>
       <c r="B10" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1592,7 +1592,7 @@
         <v>128105193</v>
       </c>
       <c r="B11" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>128105190</v>
       </c>
       <c r="B12" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         <v>128105198</v>
       </c>
       <c r="B13" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1895,7 +1895,7 @@
         <v>128105206</v>
       </c>
       <c r="B14" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1996,7 +1996,7 @@
         <v>128105202</v>
       </c>
       <c r="B15" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
         <v>128105181</v>
       </c>
       <c r="B16" t="n">
-        <v>80169</v>
+        <v>80173</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2198,7 +2198,7 @@
         <v>128105203</v>
       </c>
       <c r="B17" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2299,7 +2299,7 @@
         <v>128105201</v>
       </c>
       <c r="B18" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2400,7 +2400,7 @@
         <v>128105196</v>
       </c>
       <c r="B19" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2501,7 +2501,7 @@
         <v>128105207</v>
       </c>
       <c r="B20" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2607,7 +2607,7 @@
         <v>128105200</v>
       </c>
       <c r="B21" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2708,7 +2708,7 @@
         <v>128105180</v>
       </c>
       <c r="B22" t="n">
-        <v>57883</v>
+        <v>57885</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2809,7 +2809,7 @@
         <v>128105204</v>
       </c>
       <c r="B23" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2910,7 +2910,7 @@
         <v>128105208</v>
       </c>
       <c r="B24" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3011,7 +3011,7 @@
         <v>128105197</v>
       </c>
       <c r="B25" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3112,7 +3112,7 @@
         <v>128105187</v>
       </c>
       <c r="B26" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3213,7 +3213,7 @@
         <v>128105189</v>
       </c>
       <c r="B27" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3314,7 +3314,7 @@
         <v>128105209</v>
       </c>
       <c r="B28" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3415,7 +3415,7 @@
         <v>128105184</v>
       </c>
       <c r="B29" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 40423-2025 artfynd.xlsx
+++ b/artfynd/A 40423-2025 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>128105178</v>
       </c>
       <c r="B3" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
         <v>128105177</v>
       </c>
       <c r="B4" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -986,7 +986,7 @@
         <v>128105195</v>
       </c>
       <c r="B5" t="n">
-        <v>91551</v>
+        <v>91558</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
         <v>128105182</v>
       </c>
       <c r="B6" t="n">
-        <v>98690</v>
+        <v>98697</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1289,7 +1289,7 @@
         <v>128105183</v>
       </c>
       <c r="B8" t="n">
-        <v>98690</v>
+        <v>98697</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1390,7 +1390,7 @@
         <v>128105191</v>
       </c>
       <c r="B9" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>128105176</v>
       </c>
       <c r="B10" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1592,7 +1592,7 @@
         <v>128105193</v>
       </c>
       <c r="B11" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>128105190</v>
       </c>
       <c r="B12" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -3112,7 +3112,7 @@
         <v>128105187</v>
       </c>
       <c r="B26" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3213,7 +3213,7 @@
         <v>128105189</v>
       </c>
       <c r="B27" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 40423-2025 artfynd.xlsx
+++ b/artfynd/A 40423-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128105199</v>
       </c>
       <c r="B2" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>128105178</v>
       </c>
       <c r="B3" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
         <v>128105177</v>
       </c>
       <c r="B4" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -986,7 +986,7 @@
         <v>128105195</v>
       </c>
       <c r="B5" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
         <v>128105182</v>
       </c>
       <c r="B6" t="n">
-        <v>98697</v>
+        <v>98699</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>128105205</v>
       </c>
       <c r="B7" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1289,7 +1289,7 @@
         <v>128105183</v>
       </c>
       <c r="B8" t="n">
-        <v>98697</v>
+        <v>98699</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1390,7 +1390,7 @@
         <v>128105191</v>
       </c>
       <c r="B9" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>128105176</v>
       </c>
       <c r="B10" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1592,7 +1592,7 @@
         <v>128105193</v>
       </c>
       <c r="B11" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>128105190</v>
       </c>
       <c r="B12" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         <v>128105198</v>
       </c>
       <c r="B13" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1895,7 +1895,7 @@
         <v>128105206</v>
       </c>
       <c r="B14" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1996,7 +1996,7 @@
         <v>128105202</v>
       </c>
       <c r="B15" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
         <v>128105181</v>
       </c>
       <c r="B16" t="n">
-        <v>80173</v>
+        <v>80175</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2198,7 +2198,7 @@
         <v>128105203</v>
       </c>
       <c r="B17" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2299,7 +2299,7 @@
         <v>128105201</v>
       </c>
       <c r="B18" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2400,7 +2400,7 @@
         <v>128105196</v>
       </c>
       <c r="B19" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2501,7 +2501,7 @@
         <v>128105207</v>
       </c>
       <c r="B20" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2607,7 +2607,7 @@
         <v>128105200</v>
       </c>
       <c r="B21" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2708,7 +2708,7 @@
         <v>128105180</v>
       </c>
       <c r="B22" t="n">
-        <v>57885</v>
+        <v>57887</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2809,7 +2809,7 @@
         <v>128105204</v>
       </c>
       <c r="B23" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2910,7 +2910,7 @@
         <v>128105208</v>
       </c>
       <c r="B24" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3011,7 +3011,7 @@
         <v>128105197</v>
       </c>
       <c r="B25" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3112,7 +3112,7 @@
         <v>128105187</v>
       </c>
       <c r="B26" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3213,7 +3213,7 @@
         <v>128105189</v>
       </c>
       <c r="B27" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3314,7 +3314,7 @@
         <v>128105209</v>
       </c>
       <c r="B28" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3415,7 +3415,7 @@
         <v>128105184</v>
       </c>
       <c r="B29" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 40423-2025 artfynd.xlsx
+++ b/artfynd/A 40423-2025 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>128105178</v>
       </c>
       <c r="B3" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
         <v>128105177</v>
       </c>
       <c r="B4" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -986,7 +986,7 @@
         <v>128105195</v>
       </c>
       <c r="B5" t="n">
-        <v>91560</v>
+        <v>91558</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
         <v>128105182</v>
       </c>
       <c r="B6" t="n">
-        <v>98699</v>
+        <v>98725</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1289,7 +1289,7 @@
         <v>128105183</v>
       </c>
       <c r="B8" t="n">
-        <v>98699</v>
+        <v>98725</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1390,7 +1390,7 @@
         <v>128105191</v>
       </c>
       <c r="B9" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>128105176</v>
       </c>
       <c r="B10" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1592,7 +1592,7 @@
         <v>128105193</v>
       </c>
       <c r="B11" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>128105190</v>
       </c>
       <c r="B12" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -3112,7 +3112,7 @@
         <v>128105187</v>
       </c>
       <c r="B26" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3213,7 +3213,7 @@
         <v>128105189</v>
       </c>
       <c r="B27" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 40423-2025 artfynd.xlsx
+++ b/artfynd/A 40423-2025 artfynd.xlsx
@@ -986,7 +986,7 @@
         <v>128105195</v>
       </c>
       <c r="B5" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1003,14 +1003,10 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1087,7 +1083,7 @@
         <v>128105182</v>
       </c>
       <c r="B6" t="n">
-        <v>98725</v>
+        <v>98726</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1289,7 +1285,7 @@
         <v>128105183</v>
       </c>
       <c r="B8" t="n">
-        <v>98725</v>
+        <v>98726</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1390,7 +1386,7 @@
         <v>128105191</v>
       </c>
       <c r="B9" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1592,7 +1588,7 @@
         <v>128105193</v>
       </c>
       <c r="B11" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1693,7 +1689,7 @@
         <v>128105190</v>
       </c>
       <c r="B12" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -3112,7 +3108,7 @@
         <v>128105187</v>
       </c>
       <c r="B26" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3213,7 +3209,7 @@
         <v>128105189</v>
       </c>
       <c r="B27" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 40423-2025 artfynd.xlsx
+++ b/artfynd/A 40423-2025 artfynd.xlsx
@@ -1083,7 +1083,7 @@
         <v>128105182</v>
       </c>
       <c r="B6" t="n">
-        <v>98726</v>
+        <v>98727</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
         <v>128105183</v>
       </c>
       <c r="B8" t="n">
-        <v>98726</v>
+        <v>98727</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1386,7 +1386,7 @@
         <v>128105191</v>
       </c>
       <c r="B9" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1588,7 +1588,7 @@
         <v>128105193</v>
       </c>
       <c r="B11" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>128105190</v>
       </c>
       <c r="B12" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -3108,7 +3108,7 @@
         <v>128105187</v>
       </c>
       <c r="B26" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3209,7 +3209,7 @@
         <v>128105189</v>
       </c>
       <c r="B27" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 40423-2025 artfynd.xlsx
+++ b/artfynd/A 40423-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128105199</v>
       </c>
       <c r="B2" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>128105178</v>
       </c>
       <c r="B3" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
         <v>128105177</v>
       </c>
       <c r="B4" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -986,7 +986,7 @@
         <v>128105195</v>
       </c>
       <c r="B5" t="n">
-        <v>91560</v>
+        <v>91563</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>128105182</v>
       </c>
       <c r="B6" t="n">
-        <v>98727</v>
+        <v>98731</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1184,7 +1184,7 @@
         <v>128105205</v>
       </c>
       <c r="B7" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
         <v>128105183</v>
       </c>
       <c r="B8" t="n">
-        <v>98727</v>
+        <v>98731</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1386,7 +1386,7 @@
         <v>128105191</v>
       </c>
       <c r="B9" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>128105176</v>
       </c>
       <c r="B10" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1588,7 +1588,7 @@
         <v>128105193</v>
       </c>
       <c r="B11" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>128105190</v>
       </c>
       <c r="B12" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1790,7 +1790,7 @@
         <v>128105198</v>
       </c>
       <c r="B13" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1891,7 +1891,7 @@
         <v>128105206</v>
       </c>
       <c r="B14" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1992,7 +1992,7 @@
         <v>128105202</v>
       </c>
       <c r="B15" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2093,7 +2093,7 @@
         <v>128105181</v>
       </c>
       <c r="B16" t="n">
-        <v>80175</v>
+        <v>80177</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2194,7 +2194,7 @@
         <v>128105203</v>
       </c>
       <c r="B17" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2295,7 +2295,7 @@
         <v>128105201</v>
       </c>
       <c r="B18" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2396,7 +2396,7 @@
         <v>128105196</v>
       </c>
       <c r="B19" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
         <v>128105207</v>
       </c>
       <c r="B20" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2603,7 +2603,7 @@
         <v>128105200</v>
       </c>
       <c r="B21" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2805,7 +2805,7 @@
         <v>128105204</v>
       </c>
       <c r="B23" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
         <v>128105208</v>
       </c>
       <c r="B24" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3007,7 +3007,7 @@
         <v>128105197</v>
       </c>
       <c r="B25" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3108,7 +3108,7 @@
         <v>128105187</v>
       </c>
       <c r="B26" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3209,7 +3209,7 @@
         <v>128105189</v>
       </c>
       <c r="B27" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3310,7 +3310,7 @@
         <v>128105209</v>
       </c>
       <c r="B28" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3411,7 +3411,7 @@
         <v>128105184</v>
       </c>
       <c r="B29" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 40423-2025 artfynd.xlsx
+++ b/artfynd/A 40423-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128105199</v>
       </c>
       <c r="B2" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>128105178</v>
       </c>
       <c r="B3" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
         <v>128105177</v>
       </c>
       <c r="B4" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -986,7 +986,7 @@
         <v>128105195</v>
       </c>
       <c r="B5" t="n">
-        <v>91563</v>
+        <v>91565</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>128105182</v>
       </c>
       <c r="B6" t="n">
-        <v>98731</v>
+        <v>98733</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1184,7 +1184,7 @@
         <v>128105205</v>
       </c>
       <c r="B7" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
         <v>128105183</v>
       </c>
       <c r="B8" t="n">
-        <v>98731</v>
+        <v>98733</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1386,7 +1386,7 @@
         <v>128105191</v>
       </c>
       <c r="B9" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>128105176</v>
       </c>
       <c r="B10" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1588,7 +1588,7 @@
         <v>128105193</v>
       </c>
       <c r="B11" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>128105190</v>
       </c>
       <c r="B12" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1790,7 +1790,7 @@
         <v>128105198</v>
       </c>
       <c r="B13" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1891,7 +1891,7 @@
         <v>128105206</v>
       </c>
       <c r="B14" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1992,7 +1992,7 @@
         <v>128105202</v>
       </c>
       <c r="B15" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2093,7 +2093,7 @@
         <v>128105181</v>
       </c>
       <c r="B16" t="n">
-        <v>80177</v>
+        <v>80178</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2194,7 +2194,7 @@
         <v>128105203</v>
       </c>
       <c r="B17" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2295,7 +2295,7 @@
         <v>128105201</v>
       </c>
       <c r="B18" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2396,7 +2396,7 @@
         <v>128105196</v>
       </c>
       <c r="B19" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
         <v>128105207</v>
       </c>
       <c r="B20" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2603,7 +2603,7 @@
         <v>128105200</v>
       </c>
       <c r="B21" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2805,7 +2805,7 @@
         <v>128105204</v>
       </c>
       <c r="B23" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
         <v>128105208</v>
       </c>
       <c r="B24" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3007,7 +3007,7 @@
         <v>128105197</v>
       </c>
       <c r="B25" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3108,7 +3108,7 @@
         <v>128105187</v>
       </c>
       <c r="B26" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3209,7 +3209,7 @@
         <v>128105189</v>
       </c>
       <c r="B27" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3310,7 +3310,7 @@
         <v>128105209</v>
       </c>
       <c r="B28" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3411,7 +3411,7 @@
         <v>128105184</v>
       </c>
       <c r="B29" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 40423-2025 artfynd.xlsx
+++ b/artfynd/A 40423-2025 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>128105178</v>
       </c>
       <c r="B3" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
         <v>128105177</v>
       </c>
       <c r="B4" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -986,7 +986,7 @@
         <v>128105195</v>
       </c>
       <c r="B5" t="n">
-        <v>91565</v>
+        <v>91569</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>128105182</v>
       </c>
       <c r="B6" t="n">
-        <v>98733</v>
+        <v>98737</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
         <v>128105183</v>
       </c>
       <c r="B8" t="n">
-        <v>98733</v>
+        <v>98737</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1386,7 +1386,7 @@
         <v>128105191</v>
       </c>
       <c r="B9" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>128105176</v>
       </c>
       <c r="B10" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1588,7 +1588,7 @@
         <v>128105193</v>
       </c>
       <c r="B11" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>128105190</v>
       </c>
       <c r="B12" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -3108,7 +3108,7 @@
         <v>128105187</v>
       </c>
       <c r="B26" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3209,7 +3209,7 @@
         <v>128105189</v>
       </c>
       <c r="B27" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 40423-2025 artfynd.xlsx
+++ b/artfynd/A 40423-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128105199</v>
+        <v>128105176</v>
       </c>
       <c r="B2" t="n">
-        <v>79044</v>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>743059</v>
+        <v>742883</v>
       </c>
       <c r="R2" t="n">
-        <v>7197601</v>
+        <v>7197635</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-08-28</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,32 +776,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128105178</v>
+        <v>128105196</v>
       </c>
       <c r="B3" t="n">
-        <v>91549</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -816,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>743047</v>
+        <v>742767</v>
       </c>
       <c r="R3" t="n">
-        <v>7197522</v>
+        <v>7197679</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -882,32 +877,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128105177</v>
+        <v>128105197</v>
       </c>
       <c r="B4" t="n">
-        <v>91549</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -917,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>743033</v>
+        <v>742882</v>
       </c>
       <c r="R4" t="n">
-        <v>7197526</v>
+        <v>7197625</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -983,30 +978,34 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128105195</v>
+        <v>128105203</v>
       </c>
       <c r="B5" t="n">
-        <v>91569</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1014,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>742779</v>
+        <v>742924</v>
       </c>
       <c r="R5" t="n">
-        <v>7197609</v>
+        <v>7197844</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1080,32 +1079,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128105182</v>
+        <v>128105204</v>
       </c>
       <c r="B6" t="n">
-        <v>98737</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1115,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>742720</v>
+        <v>742779</v>
       </c>
       <c r="R6" t="n">
-        <v>7197812</v>
+        <v>7197609</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1184,11 +1183,11 @@
         <v>128105205</v>
       </c>
       <c r="B7" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1282,32 +1281,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128105183</v>
+        <v>128105187</v>
       </c>
       <c r="B8" t="n">
-        <v>98737</v>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1317,10 +1316,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>742778</v>
+        <v>742851</v>
       </c>
       <c r="R8" t="n">
-        <v>7197616</v>
+        <v>7197885</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1383,10 +1382,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128105191</v>
+        <v>128105189</v>
       </c>
       <c r="B9" t="n">
-        <v>98716</v>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1418,10 +1417,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>742729</v>
+        <v>742836</v>
       </c>
       <c r="R9" t="n">
-        <v>7197803</v>
+        <v>7197877</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1484,32 +1483,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128105176</v>
+        <v>128105191</v>
       </c>
       <c r="B10" t="n">
-        <v>91549</v>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1519,10 +1518,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>742883</v>
+        <v>742729</v>
       </c>
       <c r="R10" t="n">
-        <v>7197635</v>
+        <v>7197803</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1585,10 +1584,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128105193</v>
+        <v>128105192</v>
       </c>
       <c r="B11" t="n">
-        <v>98716</v>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1620,10 +1619,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>742919</v>
+        <v>742777</v>
       </c>
       <c r="R11" t="n">
-        <v>7197599</v>
+        <v>7197593</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1686,10 +1685,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128105190</v>
+        <v>128105193</v>
       </c>
       <c r="B12" t="n">
-        <v>98716</v>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1721,10 +1720,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>743078</v>
+        <v>742919</v>
       </c>
       <c r="R12" t="n">
-        <v>7197587</v>
+        <v>7197599</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1787,32 +1786,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128105198</v>
+        <v>128105182</v>
       </c>
       <c r="B13" t="n">
-        <v>79044</v>
+        <v>99140</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1822,10 +1821,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>743076</v>
+        <v>742720</v>
       </c>
       <c r="R13" t="n">
-        <v>7197586</v>
+        <v>7197812</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1888,32 +1887,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128105206</v>
+        <v>128105183</v>
       </c>
       <c r="B14" t="n">
-        <v>79044</v>
+        <v>99140</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1923,10 +1922,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>743042</v>
+        <v>742778</v>
       </c>
       <c r="R14" t="n">
-        <v>7197583</v>
+        <v>7197616</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1989,10 +1988,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128105202</v>
+        <v>128105177</v>
       </c>
       <c r="B15" t="n">
-        <v>79044</v>
+        <v>91909</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2000,21 +1999,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2024,10 +2023,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>742977</v>
+        <v>743033</v>
       </c>
       <c r="R15" t="n">
-        <v>7197813</v>
+        <v>7197526</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2090,32 +2089,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128105181</v>
+        <v>128105178</v>
       </c>
       <c r="B16" t="n">
-        <v>80178</v>
+        <v>91909</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2125,10 +2124,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>742967</v>
+        <v>743047</v>
       </c>
       <c r="R16" t="n">
-        <v>7197575</v>
+        <v>7197522</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2191,14 +2190,14 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128105203</v>
+        <v>128105198</v>
       </c>
       <c r="B17" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -2226,10 +2225,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>742924</v>
+        <v>743076</v>
       </c>
       <c r="R17" t="n">
-        <v>7197844</v>
+        <v>7197586</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2292,14 +2291,14 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128105201</v>
+        <v>128105199</v>
       </c>
       <c r="B18" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -2327,10 +2326,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>743024</v>
+        <v>743059</v>
       </c>
       <c r="R18" t="n">
-        <v>7197790</v>
+        <v>7197601</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2363,6 +2362,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2393,14 +2397,14 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128105196</v>
+        <v>128105200</v>
       </c>
       <c r="B19" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -2428,10 +2432,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>742767</v>
+        <v>743052</v>
       </c>
       <c r="R19" t="n">
-        <v>7197679</v>
+        <v>7197729</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2494,14 +2498,14 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128105207</v>
+        <v>128105201</v>
       </c>
       <c r="B20" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -2529,10 +2533,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>743058</v>
+        <v>743024</v>
       </c>
       <c r="R20" t="n">
-        <v>7197514</v>
+        <v>7197790</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2565,11 +2569,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-08-28</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2600,14 +2599,14 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128105200</v>
+        <v>128105202</v>
       </c>
       <c r="B21" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -2635,10 +2634,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>743052</v>
+        <v>742977</v>
       </c>
       <c r="R21" t="n">
-        <v>7197729</v>
+        <v>7197813</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2701,32 +2700,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128105180</v>
+        <v>128105206</v>
       </c>
       <c r="B22" t="n">
-        <v>57887</v>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2739,7 +2738,7 @@
         <v>743042</v>
       </c>
       <c r="R22" t="n">
-        <v>7197499</v>
+        <v>7197583</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2802,14 +2801,14 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128105204</v>
+        <v>128105207</v>
       </c>
       <c r="B23" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -2837,10 +2836,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>742779</v>
+        <v>743058</v>
       </c>
       <c r="R23" t="n">
-        <v>7197609</v>
+        <v>7197514</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2873,6 +2872,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2906,11 +2910,11 @@
         <v>128105208</v>
       </c>
       <c r="B24" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -3004,14 +3008,14 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128105197</v>
+        <v>128105209</v>
       </c>
       <c r="B25" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -3039,10 +3043,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>742882</v>
+        <v>743101</v>
       </c>
       <c r="R25" t="n">
-        <v>7197625</v>
+        <v>7197438</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3105,32 +3109,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128105187</v>
+        <v>128105184</v>
       </c>
       <c r="B26" t="n">
-        <v>98716</v>
+        <v>80432</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3140,10 +3144,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>742851</v>
+        <v>742971</v>
       </c>
       <c r="R26" t="n">
-        <v>7197885</v>
+        <v>7197577</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3206,32 +3210,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128105189</v>
+        <v>128105181</v>
       </c>
       <c r="B27" t="n">
-        <v>98716</v>
+        <v>80461</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3241,10 +3245,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>742836</v>
+        <v>742967</v>
       </c>
       <c r="R27" t="n">
-        <v>7197877</v>
+        <v>7197575</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3307,10 +3311,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128105209</v>
+        <v>128105180</v>
       </c>
       <c r="B28" t="n">
-        <v>79044</v>
+        <v>58114</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3318,21 +3322,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3342,10 +3346,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>743101</v>
+        <v>743042</v>
       </c>
       <c r="R28" t="n">
-        <v>7197438</v>
+        <v>7197499</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3408,32 +3412,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128105184</v>
+        <v>128105190</v>
       </c>
       <c r="B29" t="n">
-        <v>80149</v>
+        <v>99118</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3443,10 +3447,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>742971</v>
+        <v>743078</v>
       </c>
       <c r="R29" t="n">
-        <v>7197577</v>
+        <v>7197587</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>

--- a/artfynd/A 40423-2025 artfynd.xlsx
+++ b/artfynd/A 40423-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ29"/>
+  <dimension ref="A1:AZ70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -786,45 +786,52 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128105196</v>
+        <v>136104649</v>
       </c>
       <c r="B3" t="n">
-        <v>79327</v>
+        <v>92027</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Oxkärrberget, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>742767</v>
+        <v>742954</v>
       </c>
       <c r="R3" t="n">
-        <v>7197679</v>
+        <v>7197702</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -851,12 +858,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -865,34 +872,31 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
-        </is>
-      </c>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128105196</t>
+          <t>https://artportalen.se/Sighting/136104649</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128105197</v>
+        <v>128105196</v>
       </c>
       <c r="B4" t="n">
         <v>79327</v>
@@ -927,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>742882</v>
+        <v>742767</v>
       </c>
       <c r="R4" t="n">
-        <v>7197625</v>
+        <v>7197679</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -992,13 +996,13 @@
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128105197</t>
+          <t>https://artportalen.se/Sighting/128105196</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128105202</v>
+        <v>128105197</v>
       </c>
       <c r="B5" t="n">
         <v>79327</v>
@@ -1033,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>742977</v>
+        <v>742882</v>
       </c>
       <c r="R5" t="n">
-        <v>7197813</v>
+        <v>7197625</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1098,13 +1102,13 @@
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128105202</t>
+          <t>https://artportalen.se/Sighting/128105197</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128105203</v>
+        <v>128105202</v>
       </c>
       <c r="B6" t="n">
         <v>79327</v>
@@ -1139,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>742924</v>
+        <v>742977</v>
       </c>
       <c r="R6" t="n">
-        <v>7197844</v>
+        <v>7197813</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1204,13 +1208,13 @@
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128105203</t>
+          <t>https://artportalen.se/Sighting/128105202</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128105204</v>
+        <v>128105203</v>
       </c>
       <c r="B7" t="n">
         <v>79327</v>
@@ -1245,10 +1249,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>742779</v>
+        <v>742924</v>
       </c>
       <c r="R7" t="n">
-        <v>7197609</v>
+        <v>7197844</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1310,13 +1314,13 @@
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128105204</t>
+          <t>https://artportalen.se/Sighting/128105203</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128105205</v>
+        <v>128105204</v>
       </c>
       <c r="B8" t="n">
         <v>79327</v>
@@ -1351,10 +1355,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>742831</v>
+        <v>742779</v>
       </c>
       <c r="R8" t="n">
-        <v>7197554</v>
+        <v>7197609</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1416,38 +1420,38 @@
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128105205</t>
+          <t>https://artportalen.se/Sighting/128105204</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128105184</v>
+        <v>128105205</v>
       </c>
       <c r="B9" t="n">
-        <v>80432</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1457,10 +1461,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>742971</v>
+        <v>742831</v>
       </c>
       <c r="R9" t="n">
-        <v>7197577</v>
+        <v>7197554</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1522,51 +1526,58 @@
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128105184</t>
+          <t>https://artportalen.se/Sighting/128105205</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128105181</v>
+        <v>136105484</v>
       </c>
       <c r="B10" t="n">
-        <v>80461</v>
+        <v>79443</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Oxkärrberget, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>742967</v>
+        <v>742821</v>
       </c>
       <c r="R10" t="n">
-        <v>7197575</v>
+        <v>7197732</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,12 +1604,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1607,37 +1618,34 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
-        </is>
-      </c>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128105181</t>
+          <t>https://artportalen.se/Sighting/136105484</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128105187</v>
+        <v>136105527</v>
       </c>
       <c r="B11" t="n">
-        <v>99118</v>
+        <v>79443</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1645,34 +1653,41 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Oxkärrberget, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>742851</v>
+        <v>742888</v>
       </c>
       <c r="R11" t="n">
-        <v>7197885</v>
+        <v>7197660</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1699,12 +1714,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1713,59 +1728,56 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
-        </is>
-      </c>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128105187</t>
+          <t>https://artportalen.se/Sighting/136105527</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128105189</v>
+        <v>128105184</v>
       </c>
       <c r="B12" t="n">
-        <v>99118</v>
+        <v>80432</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1775,10 +1787,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>742836</v>
+        <v>742971</v>
       </c>
       <c r="R12" t="n">
-        <v>7197877</v>
+        <v>7197577</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1840,51 +1852,58 @@
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128105189</t>
+          <t>https://artportalen.se/Sighting/128105184</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128105191</v>
+        <v>136105627</v>
       </c>
       <c r="B13" t="n">
-        <v>99118</v>
+        <v>80558</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Oxkärrberget, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>742729</v>
+        <v>742967</v>
       </c>
       <c r="R13" t="n">
-        <v>7197803</v>
+        <v>7197572</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1911,12 +1930,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>på gammal sälg</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1925,59 +1949,56 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
-        </is>
-      </c>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128105191</t>
+          <t>https://artportalen.se/Sighting/136105627</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128105192</v>
+        <v>128105181</v>
       </c>
       <c r="B14" t="n">
-        <v>99118</v>
+        <v>80461</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1987,10 +2008,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>742777</v>
+        <v>742967</v>
       </c>
       <c r="R14" t="n">
-        <v>7197593</v>
+        <v>7197575</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2052,51 +2073,59 @@
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128105192</t>
+          <t>https://artportalen.se/Sighting/128105181</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128105193</v>
+        <v>136104873</v>
       </c>
       <c r="B15" t="n">
-        <v>99118</v>
+        <v>57982</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Oxkärrberget, Vb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>742919</v>
+        <v>742806</v>
       </c>
       <c r="R15" t="n">
-        <v>7197599</v>
+        <v>7197879</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2123,19 +2152,24 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
         </is>
       </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG15" t="b">
         <v>0</v>
@@ -2143,66 +2177,70 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
-        </is>
-      </c>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128105193</t>
+          <t>https://artportalen.se/Sighting/136104873</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128105182</v>
+        <v>136105135</v>
       </c>
       <c r="B16" t="n">
-        <v>99140</v>
+        <v>57982</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Oxkärrberget, Vb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>742720</v>
+        <v>742806</v>
       </c>
       <c r="R16" t="n">
-        <v>7197812</v>
+        <v>7197747</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2229,19 +2267,24 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
         </is>
       </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG16" t="b">
         <v>0</v>
@@ -2249,66 +2292,66 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
-        </is>
-      </c>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128105182</t>
+          <t>https://artportalen.se/Sighting/136105135</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128105183</v>
+        <v>136104964</v>
       </c>
       <c r="B17" t="n">
-        <v>99140</v>
+        <v>58143</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221952</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Oxkärrberget, Vb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>742778</v>
+        <v>742745</v>
       </c>
       <c r="R17" t="n">
-        <v>7197616</v>
+        <v>7197874</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2335,12 +2378,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2355,31 +2398,27 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
-        </is>
-      </c>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128105183</t>
+          <t>https://artportalen.se/Sighting/136104964</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128105177</v>
+        <v>136105595</v>
       </c>
       <c r="B18" t="n">
-        <v>91909</v>
+        <v>58143</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2387,34 +2426,38 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Oxkärrberget, Vb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>743033</v>
+        <v>742945</v>
       </c>
       <c r="R18" t="n">
-        <v>7197526</v>
+        <v>7197590</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2441,12 +2484,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2461,53 +2504,49 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
-        </is>
-      </c>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128105177</t>
+          <t>https://artportalen.se/Sighting/136105595</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128105178</v>
+        <v>128105187</v>
       </c>
       <c r="B19" t="n">
-        <v>91909</v>
+        <v>99118</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2517,10 +2556,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>743047</v>
+        <v>742851</v>
       </c>
       <c r="R19" t="n">
-        <v>7197522</v>
+        <v>7197885</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2582,16 +2621,16 @@
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128105178</t>
+          <t>https://artportalen.se/Sighting/128105187</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128105198</v>
+        <v>128105189</v>
       </c>
       <c r="B20" t="n">
-        <v>79327</v>
+        <v>99118</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2599,21 +2638,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2623,10 +2662,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>743076</v>
+        <v>742836</v>
       </c>
       <c r="R20" t="n">
-        <v>7197586</v>
+        <v>7197877</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2688,16 +2727,16 @@
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128105198</t>
+          <t>https://artportalen.se/Sighting/128105189</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128105199</v>
+        <v>128105191</v>
       </c>
       <c r="B21" t="n">
-        <v>79327</v>
+        <v>99118</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2705,21 +2744,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2729,10 +2768,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>743059</v>
+        <v>742729</v>
       </c>
       <c r="R21" t="n">
-        <v>7197601</v>
+        <v>7197803</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2767,11 +2806,6 @@
           <t>2025-08-28</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Med apothecier</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -2799,16 +2833,16 @@
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128105199</t>
+          <t>https://artportalen.se/Sighting/128105191</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128105200</v>
+        <v>128105192</v>
       </c>
       <c r="B22" t="n">
-        <v>79327</v>
+        <v>99118</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2816,21 +2850,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2840,10 +2874,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>743052</v>
+        <v>742777</v>
       </c>
       <c r="R22" t="n">
-        <v>7197729</v>
+        <v>7197593</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2905,16 +2939,16 @@
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128105200</t>
+          <t>https://artportalen.se/Sighting/128105192</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128105201</v>
+        <v>128105193</v>
       </c>
       <c r="B23" t="n">
-        <v>79327</v>
+        <v>99118</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2922,21 +2956,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2946,10 +2980,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>743024</v>
+        <v>742919</v>
       </c>
       <c r="R23" t="n">
-        <v>7197790</v>
+        <v>7197599</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3011,16 +3045,16 @@
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128105201</t>
+          <t>https://artportalen.se/Sighting/128105193</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128105206</v>
+        <v>136104682</v>
       </c>
       <c r="B24" t="n">
-        <v>79327</v>
+        <v>99293</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3028,34 +3062,46 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Oxkärrberget, Vb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>743042</v>
+        <v>742849</v>
       </c>
       <c r="R24" t="n">
-        <v>7197583</v>
+        <v>7197884</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3082,12 +3128,17 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>två snart överblommade</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3096,37 +3147,34 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
-        </is>
-      </c>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128105206</t>
+          <t>https://artportalen.se/Sighting/136104682</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128105207</v>
+        <v>136104742</v>
       </c>
       <c r="B25" t="n">
-        <v>79327</v>
+        <v>99293</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3134,34 +3182,42 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Oxkärrberget, Vb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>743058</v>
+        <v>742842</v>
       </c>
       <c r="R25" t="n">
-        <v>7197514</v>
+        <v>7197870</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3188,17 +3244,17 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Långa bålar</t>
+          <t>ca 10st överblommade</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3207,37 +3263,34 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
-        </is>
-      </c>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128105207</t>
+          <t>https://artportalen.se/Sighting/136104742</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128105208</v>
+        <v>136104802</v>
       </c>
       <c r="B26" t="n">
-        <v>79327</v>
+        <v>99293</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3245,34 +3298,42 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Oxkärrberget, Vb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>743053</v>
+        <v>742837</v>
       </c>
       <c r="R26" t="n">
-        <v>7197486</v>
+        <v>7197867</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3299,12 +3360,17 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>ca 10 st överblommade</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3313,37 +3379,34 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AY26" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
-        </is>
-      </c>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128105208</t>
+          <t>https://artportalen.se/Sighting/136104802</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128105209</v>
+        <v>136104805</v>
       </c>
       <c r="B27" t="n">
-        <v>79327</v>
+        <v>99293</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3351,34 +3414,42 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Oxkärrberget, Vb</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>743101</v>
+        <v>742833</v>
       </c>
       <c r="R27" t="n">
-        <v>7197438</v>
+        <v>7197861</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3405,12 +3476,17 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>ca 10st överblommade</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3419,72 +3495,73 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AY27" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
-        </is>
-      </c>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128105209</t>
+          <t>https://artportalen.se/Sighting/136104805</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128105180</v>
+        <v>136104810</v>
       </c>
       <c r="B28" t="n">
-        <v>58114</v>
+        <v>99293</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Oxkärrberget, Vb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>743042</v>
+        <v>742827</v>
       </c>
       <c r="R28" t="n">
-        <v>7197499</v>
+        <v>7197872</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3511,12 +3588,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3525,37 +3602,34 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AY28" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
-        </is>
-      </c>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128105180</t>
+          <t>https://artportalen.se/Sighting/136104810</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128105190</v>
+        <v>136104817</v>
       </c>
       <c r="B29" t="n">
-        <v>99118</v>
+        <v>99293</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3581,16 +3655,24 @@
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Oxkärrberget, Vb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>743078</v>
+        <v>742815</v>
       </c>
       <c r="R29" t="n">
-        <v>7197587</v>
+        <v>7197875</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3617,12 +3699,17 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>mycket rik förekomst - ca 100st överblommade!</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3631,28 +3718,4494 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136104817</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>136104896</v>
+      </c>
+      <c r="B30" t="n">
+        <v>99293</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Oxkärrberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>742792</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7197879</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136104896</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>136104915</v>
+      </c>
+      <c r="B31" t="n">
+        <v>99293</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Oxkärrberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>742784</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7197868</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136104915</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>136104933</v>
+      </c>
+      <c r="B32" t="n">
+        <v>99293</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Oxkärrberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>742765</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7197865</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136104933</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>136104945</v>
+      </c>
+      <c r="B33" t="n">
+        <v>99293</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Oxkärrberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>742762</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7197862</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136104945</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>136105052</v>
+      </c>
+      <c r="B34" t="n">
+        <v>99293</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Oxkärrberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>742746</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7197836</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136105052</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>136105065</v>
+      </c>
+      <c r="B35" t="n">
+        <v>99293</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Oxkärrberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>742744</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7197823</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136105065</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>136105086</v>
+      </c>
+      <c r="B36" t="n">
+        <v>99293</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Oxkärrberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>742750</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7197806</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136105086</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>136105095</v>
+      </c>
+      <c r="B37" t="n">
+        <v>99293</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Oxkärrberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>742791</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7197752</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136105095</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>128105182</v>
+      </c>
+      <c r="B38" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Oxkärrberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>742720</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7197812</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AX29" t="inlineStr">
+      <c r="AX38" t="inlineStr">
         <is>
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY29" t="inlineStr">
+      <c r="AY38" t="inlineStr">
         <is>
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
-      <c r="AZ29" t="inlineStr">
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128105182</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>128105183</v>
+      </c>
+      <c r="B39" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Oxkärrberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>742778</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7197616</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128105183</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>128105177</v>
+      </c>
+      <c r="B40" t="n">
+        <v>91909</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Oxkärrberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>743033</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7197526</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128105177</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>128105178</v>
+      </c>
+      <c r="B41" t="n">
+        <v>91909</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Oxkärrberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>743047</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7197522</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128105178</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>136104590</v>
+      </c>
+      <c r="B42" t="n">
+        <v>92064</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Oxkärrberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>743025</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7197633</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF42" t="inlineStr"/>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136104590</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>128105198</v>
+      </c>
+      <c r="B43" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Oxkärrberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>743076</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7197586</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128105198</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>128105199</v>
+      </c>
+      <c r="B44" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Oxkärrberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>743059</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7197601</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Med apothecier</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128105199</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>128105200</v>
+      </c>
+      <c r="B45" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Oxkärrberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>743052</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7197729</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128105200</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>128105201</v>
+      </c>
+      <c r="B46" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Oxkärrberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>743024</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7197790</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128105201</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>128105206</v>
+      </c>
+      <c r="B47" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Oxkärrberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>743042</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7197583</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128105206</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>128105207</v>
+      </c>
+      <c r="B48" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Oxkärrberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>743058</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7197514</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Långa bålar</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128105207</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>128105208</v>
+      </c>
+      <c r="B49" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Oxkärrberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>743053</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7197486</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128105208</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>128105209</v>
+      </c>
+      <c r="B50" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Oxkärrberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>743101</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7197438</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128105209</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>136104521</v>
+      </c>
+      <c r="B51" t="n">
+        <v>79443</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Oxkärrberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>743103</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7197577</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF51" t="inlineStr"/>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136104521</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>136104536</v>
+      </c>
+      <c r="B52" t="n">
+        <v>79443</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Oxkärrberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>743090</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7197585</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF52" t="inlineStr"/>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136104536</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>136104608</v>
+      </c>
+      <c r="B53" t="n">
+        <v>79443</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Oxkärrberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>743018</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7197638</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF53" t="inlineStr"/>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136104608</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>136104622</v>
+      </c>
+      <c r="B54" t="n">
+        <v>79443</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Oxkärrberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>743002</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7197676</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF54" t="inlineStr"/>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136104622</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>136104557</v>
+      </c>
+      <c r="B55" t="n">
+        <v>57982</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Oxkärrberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>743046</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7197611</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136104557</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>136106452</v>
+      </c>
+      <c r="B56" t="n">
+        <v>57982</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Oxkärrberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>743114</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7197609</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136106452</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>136106502</v>
+      </c>
+      <c r="B57" t="n">
+        <v>57982</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Oxkärrberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>743116</v>
+      </c>
+      <c r="R57" t="n">
+        <v>7197620</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>äldre ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136106502</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>128105180</v>
+      </c>
+      <c r="B58" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Oxkärrberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>743042</v>
+      </c>
+      <c r="R58" t="n">
+        <v>7197499</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128105180</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>136105936</v>
+      </c>
+      <c r="B59" t="n">
+        <v>98314</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>219815</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Ekbräken</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Gymnocarpium dryopteris</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(L.) Newman</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Oxkärrberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>743038</v>
+      </c>
+      <c r="R59" t="n">
+        <v>7197582</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF59" t="inlineStr"/>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136105936</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>136105887</v>
+      </c>
+      <c r="B60" t="n">
+        <v>108387</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>220102</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Kärrfibbla</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Crepis paludosa</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(L.) Moench</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Oxkärrberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>743038</v>
+      </c>
+      <c r="R60" t="n">
+        <v>7197582</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF60" t="inlineStr"/>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136105887</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>128105190</v>
+      </c>
+      <c r="B61" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Oxkärrberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>743078</v>
+      </c>
+      <c r="R61" t="n">
+        <v>7197587</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
+      <c r="AZ61" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/128105190</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>136105647</v>
+      </c>
+      <c r="B62" t="n">
+        <v>99293</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Oxkärrberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>743027</v>
+      </c>
+      <c r="R62" t="n">
+        <v>7197597</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF62" t="inlineStr"/>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136105647</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>136105659</v>
+      </c>
+      <c r="B63" t="n">
+        <v>99293</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Oxkärrberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>743024</v>
+      </c>
+      <c r="R63" t="n">
+        <v>7197592</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>rik förekomst, ca 50st överblommade</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF63" t="inlineStr"/>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136105659</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>136105724</v>
+      </c>
+      <c r="B64" t="n">
+        <v>99293</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Oxkärrberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>743020</v>
+      </c>
+      <c r="R64" t="n">
+        <v>7197582</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF64" t="inlineStr"/>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136105724</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>136105742</v>
+      </c>
+      <c r="B65" t="n">
+        <v>99293</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Oxkärrberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>743025</v>
+      </c>
+      <c r="R65" t="n">
+        <v>7197583</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF65" t="inlineStr"/>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136105742</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>136105761</v>
+      </c>
+      <c r="B66" t="n">
+        <v>99293</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Oxkärrberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>743013</v>
+      </c>
+      <c r="R66" t="n">
+        <v>7197581</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF66" t="inlineStr"/>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136105761</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>136105770</v>
+      </c>
+      <c r="B67" t="n">
+        <v>99293</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Oxkärrberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>743007</v>
+      </c>
+      <c r="R67" t="n">
+        <v>7197580</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF67" t="inlineStr"/>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136105770</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>136105806</v>
+      </c>
+      <c r="B68" t="n">
+        <v>99293</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Oxkärrberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>743009</v>
+      </c>
+      <c r="R68" t="n">
+        <v>7197576</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>rikligt med överblommade exemplar</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF68" t="inlineStr"/>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136105806</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>136105844</v>
+      </c>
+      <c r="B69" t="n">
+        <v>99293</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Oxkärrberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>743013</v>
+      </c>
+      <c r="R69" t="n">
+        <v>7197571</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>rik förekomst!</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF69" t="inlineStr"/>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136105844</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>136106137</v>
+      </c>
+      <c r="B70" t="n">
+        <v>99293</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Oxkärrberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>743057</v>
+      </c>
+      <c r="R70" t="n">
+        <v>7197580</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF70" t="inlineStr"/>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136106137</t>
         </is>
       </c>
     </row>
@@ -3686,6 +8239,47 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 40423-2025 artfynd.xlsx
+++ b/artfynd/A 40423-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136104649</v>
       </c>
       <c r="B3" t="n">
-        <v>92027</v>
+        <v>92028</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1535,7 +1535,7 @@
         <v>136105484</v>
       </c>
       <c r="B10" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1645,7 +1645,7 @@
         <v>136105527</v>
       </c>
       <c r="B11" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>136105627</v>
       </c>
       <c r="B13" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -3054,7 +3054,7 @@
         <v>136104682</v>
       </c>
       <c r="B24" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3174,7 +3174,7 @@
         <v>136104742</v>
       </c>
       <c r="B25" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3290,7 +3290,7 @@
         <v>136104802</v>
       </c>
       <c r="B26" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3406,7 +3406,7 @@
         <v>136104805</v>
       </c>
       <c r="B27" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3522,7 +3522,7 @@
         <v>136104810</v>
       </c>
       <c r="B28" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3629,7 +3629,7 @@
         <v>136104817</v>
       </c>
       <c r="B29" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3745,7 +3745,7 @@
         <v>136104896</v>
       </c>
       <c r="B30" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3856,7 +3856,7 @@
         <v>136104915</v>
       </c>
       <c r="B31" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3967,7 +3967,7 @@
         <v>136104933</v>
       </c>
       <c r="B32" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4074,7 +4074,7 @@
         <v>136104945</v>
       </c>
       <c r="B33" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4181,7 +4181,7 @@
         <v>136105052</v>
       </c>
       <c r="B34" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4292,7 +4292,7 @@
         <v>136105065</v>
       </c>
       <c r="B35" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4399,7 +4399,7 @@
         <v>136105086</v>
       </c>
       <c r="B36" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4506,7 +4506,7 @@
         <v>136105095</v>
       </c>
       <c r="B37" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5037,7 +5037,7 @@
         <v>136104590</v>
       </c>
       <c r="B42" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         <v>136104521</v>
       </c>
       <c r="B51" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6115,7 +6115,7 @@
         <v>136104536</v>
       </c>
       <c r="B52" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6225,7 +6225,7 @@
         <v>136104608</v>
       </c>
       <c r="B53" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6335,7 +6335,7 @@
         <v>136104622</v>
       </c>
       <c r="B54" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6896,7 +6896,7 @@
         <v>136105936</v>
       </c>
       <c r="B59" t="n">
-        <v>98314</v>
+        <v>98315</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7007,7 +7007,7 @@
         <v>136105887</v>
       </c>
       <c r="B60" t="n">
-        <v>108387</v>
+        <v>108389</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7224,7 +7224,7 @@
         <v>136105647</v>
       </c>
       <c r="B62" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7331,7 +7331,7 @@
         <v>136105659</v>
       </c>
       <c r="B63" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7447,7 +7447,7 @@
         <v>136105724</v>
       </c>
       <c r="B64" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7554,7 +7554,7 @@
         <v>136105742</v>
       </c>
       <c r="B65" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7661,7 +7661,7 @@
         <v>136105761</v>
       </c>
       <c r="B66" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7772,7 +7772,7 @@
         <v>136105770</v>
       </c>
       <c r="B67" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         <v>136105806</v>
       </c>
       <c r="B68" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7995,7 +7995,7 @@
         <v>136105844</v>
       </c>
       <c r="B69" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8107,7 +8107,7 @@
         <v>136106137</v>
       </c>
       <c r="B70" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>

--- a/artfynd/A 40423-2025 artfynd.xlsx
+++ b/artfynd/A 40423-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136104649</v>
       </c>
       <c r="B3" t="n">
-        <v>92028</v>
+        <v>92029</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -3054,7 +3054,7 @@
         <v>136104682</v>
       </c>
       <c r="B24" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3174,7 +3174,7 @@
         <v>136104742</v>
       </c>
       <c r="B25" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3290,7 +3290,7 @@
         <v>136104802</v>
       </c>
       <c r="B26" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3406,7 +3406,7 @@
         <v>136104805</v>
       </c>
       <c r="B27" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3522,7 +3522,7 @@
         <v>136104810</v>
       </c>
       <c r="B28" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3629,7 +3629,7 @@
         <v>136104817</v>
       </c>
       <c r="B29" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3745,7 +3745,7 @@
         <v>136104896</v>
       </c>
       <c r="B30" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3856,7 +3856,7 @@
         <v>136104915</v>
       </c>
       <c r="B31" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3967,7 +3967,7 @@
         <v>136104933</v>
       </c>
       <c r="B32" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4074,7 +4074,7 @@
         <v>136104945</v>
       </c>
       <c r="B33" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4181,7 +4181,7 @@
         <v>136105052</v>
       </c>
       <c r="B34" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4292,7 +4292,7 @@
         <v>136105065</v>
       </c>
       <c r="B35" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4399,7 +4399,7 @@
         <v>136105086</v>
       </c>
       <c r="B36" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4506,7 +4506,7 @@
         <v>136105095</v>
       </c>
       <c r="B37" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5037,7 +5037,7 @@
         <v>136104590</v>
       </c>
       <c r="B42" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -6896,7 +6896,7 @@
         <v>136105936</v>
       </c>
       <c r="B59" t="n">
-        <v>98315</v>
+        <v>98316</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7007,7 +7007,7 @@
         <v>136105887</v>
       </c>
       <c r="B60" t="n">
-        <v>108389</v>
+        <v>108390</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7224,7 +7224,7 @@
         <v>136105647</v>
       </c>
       <c r="B62" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7331,7 +7331,7 @@
         <v>136105659</v>
       </c>
       <c r="B63" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7447,7 +7447,7 @@
         <v>136105724</v>
       </c>
       <c r="B64" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7554,7 +7554,7 @@
         <v>136105742</v>
       </c>
       <c r="B65" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7661,7 +7661,7 @@
         <v>136105761</v>
       </c>
       <c r="B66" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7772,7 +7772,7 @@
         <v>136105770</v>
       </c>
       <c r="B67" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         <v>136105806</v>
       </c>
       <c r="B68" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7995,7 +7995,7 @@
         <v>136105844</v>
       </c>
       <c r="B69" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8107,7 +8107,7 @@
         <v>136106137</v>
       </c>
       <c r="B70" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>

--- a/artfynd/A 40423-2025 artfynd.xlsx
+++ b/artfynd/A 40423-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136104649</v>
       </c>
       <c r="B3" t="n">
-        <v>92029</v>
+        <v>92030</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1535,7 +1535,7 @@
         <v>136105484</v>
       </c>
       <c r="B10" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1645,7 +1645,7 @@
         <v>136105527</v>
       </c>
       <c r="B11" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>136105627</v>
       </c>
       <c r="B13" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2082,7 +2082,7 @@
         <v>136104873</v>
       </c>
       <c r="B15" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2197,7 +2197,7 @@
         <v>136105135</v>
       </c>
       <c r="B16" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2312,7 +2312,7 @@
         <v>136104964</v>
       </c>
       <c r="B17" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2418,7 +2418,7 @@
         <v>136105595</v>
       </c>
       <c r="B18" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3054,7 +3054,7 @@
         <v>136104682</v>
       </c>
       <c r="B24" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3174,7 +3174,7 @@
         <v>136104742</v>
       </c>
       <c r="B25" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3290,7 +3290,7 @@
         <v>136104802</v>
       </c>
       <c r="B26" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3406,7 +3406,7 @@
         <v>136104805</v>
       </c>
       <c r="B27" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3522,7 +3522,7 @@
         <v>136104810</v>
       </c>
       <c r="B28" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3629,7 +3629,7 @@
         <v>136104817</v>
       </c>
       <c r="B29" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3745,7 +3745,7 @@
         <v>136104896</v>
       </c>
       <c r="B30" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3856,7 +3856,7 @@
         <v>136104915</v>
       </c>
       <c r="B31" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3967,7 +3967,7 @@
         <v>136104933</v>
       </c>
       <c r="B32" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4074,7 +4074,7 @@
         <v>136104945</v>
       </c>
       <c r="B33" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4181,7 +4181,7 @@
         <v>136105052</v>
       </c>
       <c r="B34" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4292,7 +4292,7 @@
         <v>136105065</v>
       </c>
       <c r="B35" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4399,7 +4399,7 @@
         <v>136105086</v>
       </c>
       <c r="B36" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4506,7 +4506,7 @@
         <v>136105095</v>
       </c>
       <c r="B37" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5037,7 +5037,7 @@
         <v>136104590</v>
       </c>
       <c r="B42" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         <v>136104521</v>
       </c>
       <c r="B51" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6115,7 +6115,7 @@
         <v>136104536</v>
       </c>
       <c r="B52" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6225,7 +6225,7 @@
         <v>136104608</v>
       </c>
       <c r="B53" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6335,7 +6335,7 @@
         <v>136104622</v>
       </c>
       <c r="B54" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6445,7 +6445,7 @@
         <v>136104557</v>
       </c>
       <c r="B55" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6560,7 +6560,7 @@
         <v>136106452</v>
       </c>
       <c r="B56" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6675,7 +6675,7 @@
         <v>136106502</v>
       </c>
       <c r="B57" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6896,7 +6896,7 @@
         <v>136105936</v>
       </c>
       <c r="B59" t="n">
-        <v>98316</v>
+        <v>98317</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7007,7 +7007,7 @@
         <v>136105887</v>
       </c>
       <c r="B60" t="n">
-        <v>108390</v>
+        <v>108391</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7224,7 +7224,7 @@
         <v>136105647</v>
       </c>
       <c r="B62" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7331,7 +7331,7 @@
         <v>136105659</v>
       </c>
       <c r="B63" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7447,7 +7447,7 @@
         <v>136105724</v>
       </c>
       <c r="B64" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7554,7 +7554,7 @@
         <v>136105742</v>
       </c>
       <c r="B65" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7661,7 +7661,7 @@
         <v>136105761</v>
       </c>
       <c r="B66" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7772,7 +7772,7 @@
         <v>136105770</v>
       </c>
       <c r="B67" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         <v>136105806</v>
       </c>
       <c r="B68" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7995,7 +7995,7 @@
         <v>136105844</v>
       </c>
       <c r="B69" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8107,7 +8107,7 @@
         <v>136106137</v>
       </c>
       <c r="B70" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>

--- a/artfynd/A 40423-2025 artfynd.xlsx
+++ b/artfynd/A 40423-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136104649</v>
       </c>
       <c r="B3" t="n">
-        <v>92030</v>
+        <v>92036</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1535,7 +1535,7 @@
         <v>136105484</v>
       </c>
       <c r="B10" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1645,7 +1645,7 @@
         <v>136105527</v>
       </c>
       <c r="B11" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>136105627</v>
       </c>
       <c r="B13" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2082,7 +2082,7 @@
         <v>136104873</v>
       </c>
       <c r="B15" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2197,7 +2197,7 @@
         <v>136105135</v>
       </c>
       <c r="B16" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2312,7 +2312,7 @@
         <v>136104964</v>
       </c>
       <c r="B17" t="n">
-        <v>58144</v>
+        <v>58148</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2418,7 +2418,7 @@
         <v>136105595</v>
       </c>
       <c r="B18" t="n">
-        <v>58144</v>
+        <v>58148</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3054,7 +3054,7 @@
         <v>136104682</v>
       </c>
       <c r="B24" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3174,7 +3174,7 @@
         <v>136104742</v>
       </c>
       <c r="B25" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3290,7 +3290,7 @@
         <v>136104802</v>
       </c>
       <c r="B26" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3406,7 +3406,7 @@
         <v>136104805</v>
       </c>
       <c r="B27" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3522,7 +3522,7 @@
         <v>136104810</v>
       </c>
       <c r="B28" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3629,7 +3629,7 @@
         <v>136104817</v>
       </c>
       <c r="B29" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3745,7 +3745,7 @@
         <v>136104896</v>
       </c>
       <c r="B30" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3856,7 +3856,7 @@
         <v>136104915</v>
       </c>
       <c r="B31" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3967,7 +3967,7 @@
         <v>136104933</v>
       </c>
       <c r="B32" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4074,7 +4074,7 @@
         <v>136104945</v>
       </c>
       <c r="B33" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4181,7 +4181,7 @@
         <v>136105052</v>
       </c>
       <c r="B34" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4292,7 +4292,7 @@
         <v>136105065</v>
       </c>
       <c r="B35" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4399,7 +4399,7 @@
         <v>136105086</v>
       </c>
       <c r="B36" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4506,7 +4506,7 @@
         <v>136105095</v>
       </c>
       <c r="B37" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5037,7 +5037,7 @@
         <v>136104590</v>
       </c>
       <c r="B42" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         <v>136104521</v>
       </c>
       <c r="B51" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6115,7 +6115,7 @@
         <v>136104536</v>
       </c>
       <c r="B52" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6225,7 +6225,7 @@
         <v>136104608</v>
       </c>
       <c r="B53" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6335,7 +6335,7 @@
         <v>136104622</v>
       </c>
       <c r="B54" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6445,7 +6445,7 @@
         <v>136104557</v>
       </c>
       <c r="B55" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6560,7 +6560,7 @@
         <v>136106452</v>
       </c>
       <c r="B56" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6675,7 +6675,7 @@
         <v>136106502</v>
       </c>
       <c r="B57" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6896,7 +6896,7 @@
         <v>136105936</v>
       </c>
       <c r="B59" t="n">
-        <v>98317</v>
+        <v>98323</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7007,7 +7007,7 @@
         <v>136105887</v>
       </c>
       <c r="B60" t="n">
-        <v>108391</v>
+        <v>108397</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7224,7 +7224,7 @@
         <v>136105647</v>
       </c>
       <c r="B62" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7331,7 +7331,7 @@
         <v>136105659</v>
       </c>
       <c r="B63" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7447,7 +7447,7 @@
         <v>136105724</v>
       </c>
       <c r="B64" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7554,7 +7554,7 @@
         <v>136105742</v>
       </c>
       <c r="B65" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7661,7 +7661,7 @@
         <v>136105761</v>
       </c>
       <c r="B66" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7772,7 +7772,7 @@
         <v>136105770</v>
       </c>
       <c r="B67" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         <v>136105806</v>
       </c>
       <c r="B68" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7995,7 +7995,7 @@
         <v>136105844</v>
       </c>
       <c r="B69" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8107,7 +8107,7 @@
         <v>136106137</v>
       </c>
       <c r="B70" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>

--- a/artfynd/A 40423-2025 artfynd.xlsx
+++ b/artfynd/A 40423-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136104649</v>
       </c>
       <c r="B3" t="n">
-        <v>92036</v>
+        <v>92037</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1535,7 +1535,7 @@
         <v>136105484</v>
       </c>
       <c r="B10" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1645,7 +1645,7 @@
         <v>136105527</v>
       </c>
       <c r="B11" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>136105627</v>
       </c>
       <c r="B13" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2082,7 +2082,7 @@
         <v>136104873</v>
       </c>
       <c r="B15" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2197,7 +2197,7 @@
         <v>136105135</v>
       </c>
       <c r="B16" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2312,7 +2312,7 @@
         <v>136104964</v>
       </c>
       <c r="B17" t="n">
-        <v>58148</v>
+        <v>58149</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2418,7 +2418,7 @@
         <v>136105595</v>
       </c>
       <c r="B18" t="n">
-        <v>58148</v>
+        <v>58149</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3054,7 +3054,7 @@
         <v>136104682</v>
       </c>
       <c r="B24" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3174,7 +3174,7 @@
         <v>136104742</v>
       </c>
       <c r="B25" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3290,7 +3290,7 @@
         <v>136104802</v>
       </c>
       <c r="B26" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3406,7 +3406,7 @@
         <v>136104805</v>
       </c>
       <c r="B27" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3522,7 +3522,7 @@
         <v>136104810</v>
       </c>
       <c r="B28" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3629,7 +3629,7 @@
         <v>136104817</v>
       </c>
       <c r="B29" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3745,7 +3745,7 @@
         <v>136104896</v>
       </c>
       <c r="B30" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3856,7 +3856,7 @@
         <v>136104915</v>
       </c>
       <c r="B31" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3967,7 +3967,7 @@
         <v>136104933</v>
       </c>
       <c r="B32" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4074,7 +4074,7 @@
         <v>136104945</v>
       </c>
       <c r="B33" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4181,7 +4181,7 @@
         <v>136105052</v>
       </c>
       <c r="B34" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4292,7 +4292,7 @@
         <v>136105065</v>
       </c>
       <c r="B35" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4399,7 +4399,7 @@
         <v>136105086</v>
       </c>
       <c r="B36" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4506,7 +4506,7 @@
         <v>136105095</v>
       </c>
       <c r="B37" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5037,7 +5037,7 @@
         <v>136104590</v>
       </c>
       <c r="B42" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         <v>136104521</v>
       </c>
       <c r="B51" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6115,7 +6115,7 @@
         <v>136104536</v>
       </c>
       <c r="B52" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6225,7 +6225,7 @@
         <v>136104608</v>
       </c>
       <c r="B53" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6335,7 +6335,7 @@
         <v>136104622</v>
       </c>
       <c r="B54" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6445,7 +6445,7 @@
         <v>136104557</v>
       </c>
       <c r="B55" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6560,7 +6560,7 @@
         <v>136106452</v>
       </c>
       <c r="B56" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6675,7 +6675,7 @@
         <v>136106502</v>
       </c>
       <c r="B57" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6896,7 +6896,7 @@
         <v>136105936</v>
       </c>
       <c r="B59" t="n">
-        <v>98323</v>
+        <v>98324</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7007,7 +7007,7 @@
         <v>136105887</v>
       </c>
       <c r="B60" t="n">
-        <v>108397</v>
+        <v>108398</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7224,7 +7224,7 @@
         <v>136105647</v>
       </c>
       <c r="B62" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7331,7 +7331,7 @@
         <v>136105659</v>
       </c>
       <c r="B63" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7447,7 +7447,7 @@
         <v>136105724</v>
       </c>
       <c r="B64" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7554,7 +7554,7 @@
         <v>136105742</v>
       </c>
       <c r="B65" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7661,7 +7661,7 @@
         <v>136105761</v>
       </c>
       <c r="B66" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7772,7 +7772,7 @@
         <v>136105770</v>
       </c>
       <c r="B67" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         <v>136105806</v>
       </c>
       <c r="B68" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7995,7 +7995,7 @@
         <v>136105844</v>
       </c>
       <c r="B69" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8107,7 +8107,7 @@
         <v>136106137</v>
       </c>
       <c r="B70" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>

--- a/artfynd/A 40423-2025 artfynd.xlsx
+++ b/artfynd/A 40423-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136104649</v>
       </c>
       <c r="B3" t="n">
-        <v>92037</v>
+        <v>92043</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1535,7 +1535,7 @@
         <v>136105484</v>
       </c>
       <c r="B10" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1645,7 +1645,7 @@
         <v>136105527</v>
       </c>
       <c r="B11" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>136105627</v>
       </c>
       <c r="B13" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -3054,7 +3054,7 @@
         <v>136104682</v>
       </c>
       <c r="B24" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3174,7 +3174,7 @@
         <v>136104742</v>
       </c>
       <c r="B25" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3290,7 +3290,7 @@
         <v>136104802</v>
       </c>
       <c r="B26" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3406,7 +3406,7 @@
         <v>136104805</v>
       </c>
       <c r="B27" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3522,7 +3522,7 @@
         <v>136104810</v>
       </c>
       <c r="B28" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3629,7 +3629,7 @@
         <v>136104817</v>
       </c>
       <c r="B29" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3745,7 +3745,7 @@
         <v>136104896</v>
       </c>
       <c r="B30" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3856,7 +3856,7 @@
         <v>136104915</v>
       </c>
       <c r="B31" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3967,7 +3967,7 @@
         <v>136104933</v>
       </c>
       <c r="B32" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4074,7 +4074,7 @@
         <v>136104945</v>
       </c>
       <c r="B33" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4181,7 +4181,7 @@
         <v>136105052</v>
       </c>
       <c r="B34" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4292,7 +4292,7 @@
         <v>136105065</v>
       </c>
       <c r="B35" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4399,7 +4399,7 @@
         <v>136105086</v>
       </c>
       <c r="B36" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4506,7 +4506,7 @@
         <v>136105095</v>
       </c>
       <c r="B37" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5037,7 +5037,7 @@
         <v>136104590</v>
       </c>
       <c r="B42" t="n">
-        <v>92074</v>
+        <v>92080</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         <v>136104521</v>
       </c>
       <c r="B51" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6115,7 +6115,7 @@
         <v>136104536</v>
       </c>
       <c r="B52" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6225,7 +6225,7 @@
         <v>136104608</v>
       </c>
       <c r="B53" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6335,7 +6335,7 @@
         <v>136104622</v>
       </c>
       <c r="B54" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6896,7 +6896,7 @@
         <v>136105936</v>
       </c>
       <c r="B59" t="n">
-        <v>98324</v>
+        <v>98335</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7007,7 +7007,7 @@
         <v>136105887</v>
       </c>
       <c r="B60" t="n">
-        <v>108398</v>
+        <v>108409</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7224,7 +7224,7 @@
         <v>136105647</v>
       </c>
       <c r="B62" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7331,7 +7331,7 @@
         <v>136105659</v>
       </c>
       <c r="B63" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7447,7 +7447,7 @@
         <v>136105724</v>
       </c>
       <c r="B64" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7554,7 +7554,7 @@
         <v>136105742</v>
       </c>
       <c r="B65" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7661,7 +7661,7 @@
         <v>136105761</v>
       </c>
       <c r="B66" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7772,7 +7772,7 @@
         <v>136105770</v>
       </c>
       <c r="B67" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         <v>136105806</v>
       </c>
       <c r="B68" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7995,7 +7995,7 @@
         <v>136105844</v>
       </c>
       <c r="B69" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8107,7 +8107,7 @@
         <v>136106137</v>
       </c>
       <c r="B70" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>

--- a/artfynd/A 40423-2025 artfynd.xlsx
+++ b/artfynd/A 40423-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136104649</v>
       </c>
       <c r="B3" t="n">
-        <v>92043</v>
+        <v>92050</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1535,7 +1535,7 @@
         <v>136105484</v>
       </c>
       <c r="B10" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1645,7 +1645,7 @@
         <v>136105527</v>
       </c>
       <c r="B11" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>136105627</v>
       </c>
       <c r="B13" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2082,7 +2082,7 @@
         <v>136104873</v>
       </c>
       <c r="B15" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2197,7 +2197,7 @@
         <v>136105135</v>
       </c>
       <c r="B16" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2312,7 +2312,7 @@
         <v>136104964</v>
       </c>
       <c r="B17" t="n">
-        <v>58149</v>
+        <v>58154</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2418,7 +2418,7 @@
         <v>136105595</v>
       </c>
       <c r="B18" t="n">
-        <v>58149</v>
+        <v>58154</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3054,7 +3054,7 @@
         <v>136104682</v>
       </c>
       <c r="B24" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3174,7 +3174,7 @@
         <v>136104742</v>
       </c>
       <c r="B25" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3290,7 +3290,7 @@
         <v>136104802</v>
       </c>
       <c r="B26" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3406,7 +3406,7 @@
         <v>136104805</v>
       </c>
       <c r="B27" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3522,7 +3522,7 @@
         <v>136104810</v>
       </c>
       <c r="B28" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3629,7 +3629,7 @@
         <v>136104817</v>
       </c>
       <c r="B29" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3745,7 +3745,7 @@
         <v>136104896</v>
       </c>
       <c r="B30" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3856,7 +3856,7 @@
         <v>136104915</v>
       </c>
       <c r="B31" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3967,7 +3967,7 @@
         <v>136104933</v>
       </c>
       <c r="B32" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4074,7 +4074,7 @@
         <v>136104945</v>
       </c>
       <c r="B33" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4181,7 +4181,7 @@
         <v>136105052</v>
       </c>
       <c r="B34" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4292,7 +4292,7 @@
         <v>136105065</v>
       </c>
       <c r="B35" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4399,7 +4399,7 @@
         <v>136105086</v>
       </c>
       <c r="B36" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4506,7 +4506,7 @@
         <v>136105095</v>
       </c>
       <c r="B37" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5037,7 +5037,7 @@
         <v>136104590</v>
       </c>
       <c r="B42" t="n">
-        <v>92080</v>
+        <v>92087</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         <v>136104521</v>
       </c>
       <c r="B51" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6115,7 +6115,7 @@
         <v>136104536</v>
       </c>
       <c r="B52" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6225,7 +6225,7 @@
         <v>136104608</v>
       </c>
       <c r="B53" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6335,7 +6335,7 @@
         <v>136104622</v>
       </c>
       <c r="B54" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6445,7 +6445,7 @@
         <v>136104557</v>
       </c>
       <c r="B55" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6560,7 +6560,7 @@
         <v>136106452</v>
       </c>
       <c r="B56" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6675,7 +6675,7 @@
         <v>136106502</v>
       </c>
       <c r="B57" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6896,7 +6896,7 @@
         <v>136105936</v>
       </c>
       <c r="B59" t="n">
-        <v>98335</v>
+        <v>98348</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7007,7 +7007,7 @@
         <v>136105887</v>
       </c>
       <c r="B60" t="n">
-        <v>108409</v>
+        <v>108422</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7224,7 +7224,7 @@
         <v>136105647</v>
       </c>
       <c r="B62" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7331,7 +7331,7 @@
         <v>136105659</v>
       </c>
       <c r="B63" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7447,7 +7447,7 @@
         <v>136105724</v>
       </c>
       <c r="B64" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7554,7 +7554,7 @@
         <v>136105742</v>
       </c>
       <c r="B65" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7661,7 +7661,7 @@
         <v>136105761</v>
       </c>
       <c r="B66" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7772,7 +7772,7 @@
         <v>136105770</v>
       </c>
       <c r="B67" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         <v>136105806</v>
       </c>
       <c r="B68" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7995,7 +7995,7 @@
         <v>136105844</v>
       </c>
       <c r="B69" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8107,7 +8107,7 @@
         <v>136106137</v>
       </c>
       <c r="B70" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>

--- a/artfynd/A 40423-2025 artfynd.xlsx
+++ b/artfynd/A 40423-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136104649</v>
       </c>
       <c r="B3" t="n">
-        <v>92050</v>
+        <v>92051</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -3054,7 +3054,7 @@
         <v>136104682</v>
       </c>
       <c r="B24" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3174,7 +3174,7 @@
         <v>136104742</v>
       </c>
       <c r="B25" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3290,7 +3290,7 @@
         <v>136104802</v>
       </c>
       <c r="B26" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3406,7 +3406,7 @@
         <v>136104805</v>
       </c>
       <c r="B27" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3522,7 +3522,7 @@
         <v>136104810</v>
       </c>
       <c r="B28" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3629,7 +3629,7 @@
         <v>136104817</v>
       </c>
       <c r="B29" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3745,7 +3745,7 @@
         <v>136104896</v>
       </c>
       <c r="B30" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3856,7 +3856,7 @@
         <v>136104915</v>
       </c>
       <c r="B31" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3967,7 +3967,7 @@
         <v>136104933</v>
       </c>
       <c r="B32" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4074,7 +4074,7 @@
         <v>136104945</v>
       </c>
       <c r="B33" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4181,7 +4181,7 @@
         <v>136105052</v>
       </c>
       <c r="B34" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4292,7 +4292,7 @@
         <v>136105065</v>
       </c>
       <c r="B35" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4399,7 +4399,7 @@
         <v>136105086</v>
       </c>
       <c r="B36" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4506,7 +4506,7 @@
         <v>136105095</v>
       </c>
       <c r="B37" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5037,7 +5037,7 @@
         <v>136104590</v>
       </c>
       <c r="B42" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -6896,7 +6896,7 @@
         <v>136105936</v>
       </c>
       <c r="B59" t="n">
-        <v>98348</v>
+        <v>98349</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7007,7 +7007,7 @@
         <v>136105887</v>
       </c>
       <c r="B60" t="n">
-        <v>108422</v>
+        <v>108423</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7224,7 +7224,7 @@
         <v>136105647</v>
       </c>
       <c r="B62" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7331,7 +7331,7 @@
         <v>136105659</v>
       </c>
       <c r="B63" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7447,7 +7447,7 @@
         <v>136105724</v>
       </c>
       <c r="B64" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7554,7 +7554,7 @@
         <v>136105742</v>
       </c>
       <c r="B65" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7661,7 +7661,7 @@
         <v>136105761</v>
       </c>
       <c r="B66" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7772,7 +7772,7 @@
         <v>136105770</v>
       </c>
       <c r="B67" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         <v>136105806</v>
       </c>
       <c r="B68" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7995,7 +7995,7 @@
         <v>136105844</v>
       </c>
       <c r="B69" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8107,7 +8107,7 @@
         <v>136106137</v>
       </c>
       <c r="B70" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>

--- a/artfynd/A 40423-2025 artfynd.xlsx
+++ b/artfynd/A 40423-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136104649</v>
       </c>
       <c r="B3" t="n">
-        <v>92051</v>
+        <v>92064</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1535,7 +1535,7 @@
         <v>136105484</v>
       </c>
       <c r="B10" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1645,7 +1645,7 @@
         <v>136105527</v>
       </c>
       <c r="B11" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>136105627</v>
       </c>
       <c r="B13" t="n">
-        <v>80575</v>
+        <v>80588</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2082,7 +2082,7 @@
         <v>136104873</v>
       </c>
       <c r="B15" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2197,7 +2197,7 @@
         <v>136105135</v>
       </c>
       <c r="B16" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2312,7 +2312,7 @@
         <v>136104964</v>
       </c>
       <c r="B17" t="n">
-        <v>58154</v>
+        <v>58167</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2418,7 +2418,7 @@
         <v>136105595</v>
       </c>
       <c r="B18" t="n">
-        <v>58154</v>
+        <v>58167</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3054,7 +3054,7 @@
         <v>136104682</v>
       </c>
       <c r="B24" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3174,7 +3174,7 @@
         <v>136104742</v>
       </c>
       <c r="B25" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3290,7 +3290,7 @@
         <v>136104802</v>
       </c>
       <c r="B26" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3406,7 +3406,7 @@
         <v>136104805</v>
       </c>
       <c r="B27" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3522,7 +3522,7 @@
         <v>136104810</v>
       </c>
       <c r="B28" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3629,7 +3629,7 @@
         <v>136104817</v>
       </c>
       <c r="B29" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3745,7 +3745,7 @@
         <v>136104896</v>
       </c>
       <c r="B30" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3856,7 +3856,7 @@
         <v>136104915</v>
       </c>
       <c r="B31" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3967,7 +3967,7 @@
         <v>136104933</v>
       </c>
       <c r="B32" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4074,7 +4074,7 @@
         <v>136104945</v>
       </c>
       <c r="B33" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4181,7 +4181,7 @@
         <v>136105052</v>
       </c>
       <c r="B34" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4292,7 +4292,7 @@
         <v>136105065</v>
       </c>
       <c r="B35" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4399,7 +4399,7 @@
         <v>136105086</v>
       </c>
       <c r="B36" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4506,7 +4506,7 @@
         <v>136105095</v>
       </c>
       <c r="B37" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5037,7 +5037,7 @@
         <v>136104590</v>
       </c>
       <c r="B42" t="n">
-        <v>92088</v>
+        <v>92101</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         <v>136104521</v>
       </c>
       <c r="B51" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6115,7 +6115,7 @@
         <v>136104536</v>
       </c>
       <c r="B52" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6225,7 +6225,7 @@
         <v>136104608</v>
       </c>
       <c r="B53" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6335,7 +6335,7 @@
         <v>136104622</v>
       </c>
       <c r="B54" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6445,7 +6445,7 @@
         <v>136104557</v>
       </c>
       <c r="B55" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6560,7 +6560,7 @@
         <v>136106452</v>
       </c>
       <c r="B56" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6675,7 +6675,7 @@
         <v>136106502</v>
       </c>
       <c r="B57" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6896,7 +6896,7 @@
         <v>136105936</v>
       </c>
       <c r="B59" t="n">
-        <v>98349</v>
+        <v>98362</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7007,7 +7007,7 @@
         <v>136105887</v>
       </c>
       <c r="B60" t="n">
-        <v>108423</v>
+        <v>108436</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7224,7 +7224,7 @@
         <v>136105647</v>
       </c>
       <c r="B62" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7331,7 +7331,7 @@
         <v>136105659</v>
       </c>
       <c r="B63" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7447,7 +7447,7 @@
         <v>136105724</v>
       </c>
       <c r="B64" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7554,7 +7554,7 @@
         <v>136105742</v>
       </c>
       <c r="B65" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7661,7 +7661,7 @@
         <v>136105761</v>
       </c>
       <c r="B66" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7772,7 +7772,7 @@
         <v>136105770</v>
       </c>
       <c r="B67" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         <v>136105806</v>
       </c>
       <c r="B68" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7995,7 +7995,7 @@
         <v>136105844</v>
       </c>
       <c r="B69" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8107,7 +8107,7 @@
         <v>136106137</v>
       </c>
       <c r="B70" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>

--- a/artfynd/A 40423-2025 artfynd.xlsx
+++ b/artfynd/A 40423-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136104649</v>
       </c>
       <c r="B3" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1535,7 +1535,7 @@
         <v>136105484</v>
       </c>
       <c r="B10" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1645,7 +1645,7 @@
         <v>136105527</v>
       </c>
       <c r="B11" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>136105627</v>
       </c>
       <c r="B13" t="n">
-        <v>80588</v>
+        <v>80589</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -3054,7 +3054,7 @@
         <v>136104682</v>
       </c>
       <c r="B24" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3174,7 +3174,7 @@
         <v>136104742</v>
       </c>
       <c r="B25" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3290,7 +3290,7 @@
         <v>136104802</v>
       </c>
       <c r="B26" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3406,7 +3406,7 @@
         <v>136104805</v>
       </c>
       <c r="B27" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3522,7 +3522,7 @@
         <v>136104810</v>
       </c>
       <c r="B28" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3629,7 +3629,7 @@
         <v>136104817</v>
       </c>
       <c r="B29" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3745,7 +3745,7 @@
         <v>136104896</v>
       </c>
       <c r="B30" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3856,7 +3856,7 @@
         <v>136104915</v>
       </c>
       <c r="B31" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3967,7 +3967,7 @@
         <v>136104933</v>
       </c>
       <c r="B32" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4074,7 +4074,7 @@
         <v>136104945</v>
       </c>
       <c r="B33" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4181,7 +4181,7 @@
         <v>136105052</v>
       </c>
       <c r="B34" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4292,7 +4292,7 @@
         <v>136105065</v>
       </c>
       <c r="B35" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4399,7 +4399,7 @@
         <v>136105086</v>
       </c>
       <c r="B36" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4506,7 +4506,7 @@
         <v>136105095</v>
       </c>
       <c r="B37" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5037,7 +5037,7 @@
         <v>136104590</v>
       </c>
       <c r="B42" t="n">
-        <v>92101</v>
+        <v>92102</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         <v>136104521</v>
       </c>
       <c r="B51" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6115,7 +6115,7 @@
         <v>136104536</v>
       </c>
       <c r="B52" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6225,7 +6225,7 @@
         <v>136104608</v>
       </c>
       <c r="B53" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6335,7 +6335,7 @@
         <v>136104622</v>
       </c>
       <c r="B54" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6896,7 +6896,7 @@
         <v>136105936</v>
       </c>
       <c r="B59" t="n">
-        <v>98362</v>
+        <v>98363</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7007,7 +7007,7 @@
         <v>136105887</v>
       </c>
       <c r="B60" t="n">
-        <v>108436</v>
+        <v>108437</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7224,7 +7224,7 @@
         <v>136105647</v>
       </c>
       <c r="B62" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7331,7 +7331,7 @@
         <v>136105659</v>
       </c>
       <c r="B63" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7447,7 +7447,7 @@
         <v>136105724</v>
       </c>
       <c r="B64" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7554,7 +7554,7 @@
         <v>136105742</v>
       </c>
       <c r="B65" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7661,7 +7661,7 @@
         <v>136105761</v>
       </c>
       <c r="B66" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7772,7 +7772,7 @@
         <v>136105770</v>
       </c>
       <c r="B67" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         <v>136105806</v>
       </c>
       <c r="B68" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7995,7 +7995,7 @@
         <v>136105844</v>
       </c>
       <c r="B69" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8107,7 +8107,7 @@
         <v>136106137</v>
       </c>
       <c r="B70" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
